--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0018.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0018.xlsx
@@ -1154,7 +1154,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Tấn Công {0} và tăng {1} Sát Thương Resonance Liberation trong {2} giây.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng tăng ATK {0} và tăng {1} Sát Thương Giải Cứu Cộng Hưởng trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Lightning Execution&lt;/color&gt;&lt;/size&gt;
 Sử dụng Resonance Skill sau khi dùng Resonance Skill &lt;color=Highlight&gt;Magnetic Roar&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Lightning Execution&lt;/color&gt;, tấn công mục tiêu và gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Nếu Resonance Skill &lt;color=Highlight&gt;Lightning Execution&lt;/color&gt; không được kích hoạt trong một khoảng thời gian hoặc Character này bị thay ra, Kỹ Năng sẽ bị đưa vào Cooldown chiêu.</t>
+Nếu Resonance Skill &lt;color=Highlight&gt;Lightning Execution&lt;/color&gt; không được kích hoạt trong một khoảng thời gian hoặc Character này bị thay ra, Kỹ Năng sẽ bị đưa vào Thời gian hồi chiêu.</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
 Tiêu hao {1} Nhụy Crimson sẽ hồi {2} Concerto Energy và nhận được &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; Nụ Crimson (thời gian tồn tại {4}s, tối đa chồng chất {5} lần).
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Forte Circuit: Ephemeral&lt;/color&gt;&lt;/size&gt;
-Khi Concerto Energy hồi đầy và &lt;color=Highlight&gt;Ephemeral&lt;/color&gt; không trong Cooldown chiêu, Resonance Skill sẽ được thay thế bằng &lt;color=Highlight&gt;Ephemeral&lt;/color&gt;.
+Khi Concerto Energy hồi đầy và &lt;color=Highlight&gt;Ephemeral&lt;/color&gt; không trong Thời gian hồi chiêu, Resonance Skill sẽ được thay thế bằng &lt;color=Highlight&gt;Ephemeral&lt;/color&gt;.
 Sử dụng &lt;color=Highlight&gt;Ephemeral&lt;/color&gt; tiêu hao {6} Concerto Energy và gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; lên mục tiêu. Loại sát thương này được tính là Sát Thương Kỹ Năng Basic.
 Sau khi sử dụng &lt;color=Highlight&gt;Budding Mode&lt;/color&gt;, Camellya sẽ bước vào trạng thái &lt;color=Highlight&gt;Ephemeral&lt;/color&gt;.
 Có thể sử dụng khi đang ở trên không.
@@ -3140,7 +3140,7 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>Calcharo thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-Nếu Calcharo rời khỏi chiến trường hoặc Resonance Skill &lt;color=Highlight&gt;Extermination Order&lt;/color&gt; không được kích hoạt lại sau một thời gian, kỹ năng này sẽ bước vào Cooldown chiêu.
+Nếu Calcharo rời khỏi chiến trường hoặc Resonance Skill &lt;color=Highlight&gt;Extermination Order&lt;/color&gt; không được kích hoạt lại sau một thời gian, kỹ năng này sẽ bước vào Thời gian hồi chiêu.
 Resonance Skill &lt;color=Highlight&gt;Extermination Order&lt;/color&gt; không làm gián đoạn chu kỳ Basic Attack của Calcharo.</t>
         </is>
       </c>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Tấn Công {0} và tăng {1} Sát Thương Resonance Liberation trong {2} giây.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng tăng ATK {0} và tăng {1} Sát Thương Giải Cứu Cộng Hưởng trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       <c r="M146" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Beyond Imagination&lt;/color&gt;&lt;/size&gt;
-- Khi Roccia ở trạng thái &lt;color=Highlight&gt;Beyond Imagination&lt;/color&gt; với ít nhất {0} Tưởng Tượng, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} nút &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tiêu hao {0} Tưởng Tượng và tung ra Basic Attack &lt;color=Highlight&gt;Thật sự Fantasy&lt;/color&gt;.
+- Khi Roccia ở trạng thái &lt;color=Highlight&gt;Beyond Imagination&lt;/color&gt; với ít nhất {0} Tưởng Tượng, {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tiêu hao {0} Tưởng Tượng và tung ra Basic Attack &lt;color=Highlight&gt;Thật sự Fantasy&lt;/color&gt;.
 - Roccia sẽ thoát khỏi trạng thái này khi không còn ở trên không hoặc khi rời khỏi chiến trường.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Thật sự Fantasy&lt;/color&gt;&lt;/size&gt;
@@ -11199,7 +11199,7 @@
       <c r="M147" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Beyond Imagination&lt;/color&gt;&lt;/size&gt;
-- Khi Roccia ở trạng thái &lt;color=Highlight&gt;Beyond Imagination&lt;/color&gt; với ít nhất {0} Trí Tưởng, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} nút &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tiêu hao {0} Trí Tưởng và tung chiêu Basic Attack &lt;color=Highlight&gt;Thật sự Fantasy&lt;/color&gt;.
+- Khi Roccia ở trạng thái &lt;color=Highlight&gt;Beyond Imagination&lt;/color&gt; với ít nhất {0} Trí Tưởng, {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để tiêu hao {0} Trí Tưởng và tung chiêu Basic Attack &lt;color=Highlight&gt;Thật sự Fantasy&lt;/color&gt;.
 - Roccia sẽ thoát khỏi trạng thái này khi không còn ở trên không hoặc khi rời khỏi chiến trường.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Thật sự Fantasy&lt;/color&gt;&lt;/size&gt;
@@ -11563,7 +11563,7 @@
 Tập trung sức mạnh để tung đòn tấn công mục tiêu, tiêu hao STA và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Containment Tactics&lt;/color&gt;&lt;/size&gt;
-Khi &lt;te href=850018&gt;Substance&lt;/te&gt; của Carlotta đạt tối đa, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Containment Tactics&lt;/color&gt;: tiêu hao toàn bộ Chất để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và giảm Cooldown chiêu của Resonance Skill &lt;color=Highlight&gt;Art of Violence&lt;/color&gt; đi {3} giây.
+Khi &lt;te href=850018&gt;Substance&lt;/te&gt; của Carlotta đạt tối đa, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Containment Tactics&lt;/color&gt;: tiêu hao toàn bộ Chất để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và giảm Thời gian hồi chiêu của Resonance Skill &lt;color=Highlight&gt;Art of Violence&lt;/color&gt; đi {3} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; ngay sau khi tiếp đất sẽ kích hoạt &lt;color=Highlight&gt;Customary Greetings&lt;/color&gt;.
@@ -11572,7 +11572,7 @@
 Lật người qua mục tiêu và bắn bất ngờ, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để phản đòn, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Hành động này tiêu hao &lt;SapTag=6&gt;{6}&lt;/SapTag&gt; Tinh Thể Linh Hoạt.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để phản đòn, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Hành động này tiêu hao &lt;SapTag=6&gt;{6}&lt;/SapTag&gt; Tinh Thể Linh Hoạt.</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11668,7 @@
 Thực hiện đòn tấn công tích năng gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Containment Tactics&lt;/color&gt;&lt;/size&gt;
-Khi Chất Lượng của Carlotta đạt tối đa, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Containment Tactics&lt;/color&gt;: tiêu hao toàn bộ Chất Lượng để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và giảm Cooldown chiêu của Resonance Skill.
+Khi Chất Lượng của Carlotta đạt tối đa, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Containment Tactics&lt;/color&gt;: tiêu hao toàn bộ Chất Lượng để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và giảm Thời gian hồi chiêu của Resonance Skill.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Thực hiện Đòn Lao Xuống gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; ngay sau khi tiếp đất sẽ thi triển &lt;color=Highlight&gt;Customary Greetings&lt;/color&gt;.
@@ -11749,14 +11749,14 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và áp đặt &lt;color=Highlight&gt;Phân Tán&lt;/color&gt; lên mục tiêu. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; một lần nữa ngay sau đó để tung ra &lt;color=Highlight&gt;Sắc Màu Rực Rỡ&lt;/color&gt;.
+          <t>Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và áp đặt &lt;color=Highlight&gt;Phân Tán&lt;/color&gt; lên mục tiêu. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; một lần nữa ngay sau đó để tung ra &lt;color=Highlight&gt;Sắc Màu Rực Rỡ&lt;/color&gt;.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Phân Tán&lt;/color&gt;&lt;/size&gt;
 Mục tiêu bị &lt;color=Highlight&gt;Phân Tán&lt;/color&gt; sẽ bị bất động trong {1} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Sắc Màu Rực Rỡ&lt;/color&gt;&lt;/size&gt;
 Tiêu thụ toàn bộ &lt;te href=850017&gt;Pha Lê Định Hình&lt;/te&gt; và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Resonance Skill sẽ bước vào Cooldown chiêu sau một khoảng thời gian nếu &lt;color=Highlight&gt;Sắc Màu Rực Rỡ&lt;/color&gt; không được tung ra hoặc Carlotta bị thay ra khỏi chiến trường.</t>
+Resonance Skill sẽ bước vào Thời gian hồi chiêu sau một khoảng thời gian nếu &lt;color=Highlight&gt;Sắc Màu Rực Rỡ&lt;/color&gt; không được tung ra hoặc Carlotta bị thay ra khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -11828,14 +11828,14 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và áp dụng &lt;color=Highlight&gt;Phân Tán&lt;/color&gt; lên mục tiêu. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; một lần nữa ngay sau đó để thi triển &lt;color=Highlight&gt;Sắc Màu Rực Rỡ&lt;/color&gt;. 
+          <t>Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và áp dụng &lt;color=Highlight&gt;Phân Tán&lt;/color&gt; lên mục tiêu. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; một lần nữa ngay sau đó để thi triển &lt;color=Highlight&gt;Sắc Màu Rực Rỡ&lt;/color&gt;. 
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Phân Tán&lt;/color&gt;&lt;/size&gt;
 Mục tiêu bị &lt;color=Highlight&gt;Phân Tán&lt;/color&gt; sẽ bị hóa đá. 
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Sắc Màu Rực Rỡ&lt;/color&gt;&lt;/size&gt;
 Tiêu thụ toàn bộ Tinh Thể Linh Hoạt và gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-Nếu không thi triển &lt;color=Highlight&gt;Sắc Màu Rực Rỡ&lt;/color&gt; hoặc Carlotta rời khỏi chiến trường, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sẽ bước vào Cooldown chiêu.</t>
+Nếu không thi triển &lt;color=Highlight&gt;Sắc Màu Rực Rỡ&lt;/color&gt; hoặc Carlotta rời khỏi chiến trường, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sẽ bước vào Thời gian hồi chiêu.</t>
         </is>
       </c>
     </row>
@@ -12523,8 +12523,8 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Imminent Oblivion&lt;/color&gt;&lt;/size&gt;
 Carlotta kích hoạt &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; mỗi {0} giây.
-Khi Chất Lượng đạt tối đa và &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; được kích hoạt, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Chất Lượng và tung ra Heavy Attack &lt;color=Highlight&gt;Imminent Oblivion&lt;/color&gt;, sau đó &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; sẽ bước vào Cooldown chiêu.
-Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; (được tính là Sát Thương Resonance Skill), và giảm Cooldown chiêu của Resonance Skill &lt;color=Highlight&gt;Art of Violence&lt;/color&gt; đi {1} giây.
+Khi Chất Lượng đạt tối đa và &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; được kích hoạt, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Chất Lượng và tung ra Heavy Attack &lt;color=Highlight&gt;Imminent Oblivion&lt;/color&gt;, sau đó &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; sẽ bước vào Thời gian hồi chiêu.
+Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; (được tính là Sát Thương Resonance Skill), và giảm Thời gian hồi chiêu của Resonance Skill &lt;color=Highlight&gt;Art of Violence&lt;/color&gt; đi {1} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Final Bow&lt;/color&gt;&lt;/size&gt;
 Khi Chất Lượng đạt tối đa, bước vào trạng thái &lt;color=Highlight&gt;Final Bow&lt;/color&gt;.
@@ -12630,8 +12630,8 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Imminent Oblivion&lt;/color&gt;&lt;/size&gt;
 Carlotta kích hoạt &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; mỗi {0} giây.
-Khi Chất Lượng đạt tối đa và &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; được kích hoạt, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Chất Lượng và tung ra Heavy Attack &lt;color=Highlight&gt;Imminent Oblivion&lt;/color&gt;, sau đó &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; sẽ进入 Cooldown.
-Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và giảm Cooldown chiêu của Resonance Skill &lt;color=Highlight&gt;Art of Violence&lt;/color&gt; đi {1} giây.
+Khi Chất Lượng đạt tối đa và &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; được kích hoạt, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao toàn bộ Chất Lượng và tung ra Heavy Attack &lt;color=Highlight&gt;Imminent Oblivion&lt;/color&gt;, sau đó &lt;color=Highlight&gt;Tinted Crystal&lt;/color&gt; sẽ bắt đầu Thời gian hồi.
+Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và giảm Thời gian hồi chiêu của Resonance Skill &lt;color=Highlight&gt;Art of Violence&lt;/color&gt; đi {1} giây.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Final Bow&lt;/color&gt;&lt;/size&gt;
 Khi Chất Lượng đạt tối đa,vào trạng thái &lt;color=Highlight&gt;Final Bow&lt;/color&gt;.
@@ -12997,16 +12997,16 @@
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Rhapsodic Riff&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 - Sau khi thực hiện &lt;color=Highlight&gt;Stage 2&lt;/color&gt; hoặc &lt;color=Highlight&gt;Stage 4&lt;/color&gt; của Basic Attack, giữ Normal Attack để thực hiện &lt;color=Highlight&gt;Heavy Attack - Rhapsodic Riff&lt;/color&gt;.
-- Sau khi thực hiện &lt;color=Highlight&gt;Mid-air Attack Stage 4&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để thực hiện &lt;color=Highlight&gt;Heavy Attack - Rhapsodic Riff&lt;/color&gt;.
+- Sau khi thực hiện &lt;color=Highlight&gt;Mid-air Attack Stage 4&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack để thực hiện &lt;color=Highlight&gt;Heavy Attack - Rhapsodic Riff&lt;/color&gt;.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau &lt;color=Highlight&gt;Stage 1&lt;/color&gt; hoặc &lt;color=Highlight&gt;Stage 2&lt;/color&gt; của Mid-air Attack để móc vào mục tiêu bằng Grapple. Brant sẽ tấn công mục tiêu nếu tiếp cận được. Thả nút khi đang thực hiện để &lt;color=Highlight&gt;lộn ngược ra sau&lt;/color&gt; sau khi đòn đánh trúng; hoặc giữ Normal Attack để tấn công liên tục và &lt;color=Highlight&gt;lộn ngược ra sau&lt;/color&gt; sau đòn kết thúc. Brant sẽ &lt;color=Highlight&gt;flips backward&lt;/color&gt; sau &lt;color=Highlight&gt;Mid-air Attack Stage 3&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau mỗi lần &lt;color=Highlight&gt;flip&lt;/color&gt; để thực hiện giai đoạn tiếp theo của &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt;. &lt;color=Highlight&gt;Flip&lt;/color&gt; sẽ đặt lại số lần Tránh Giữa Không.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau &lt;color=Highlight&gt;Stage 1&lt;/color&gt; hoặc &lt;color=Highlight&gt;Stage 2&lt;/color&gt; của Mid-air Attack để móc vào mục tiêu bằng Grapple. Brant sẽ tấn công mục tiêu nếu tiếp cận được. Thả nút khi đang thực hiện để &lt;color=Highlight&gt;lộn ngược ra sau&lt;/color&gt; sau khi đòn đánh trúng; hoặc giữ Normal Attack để tấn công liên tục và &lt;color=Highlight&gt;lộn ngược ra sau&lt;/color&gt; sau đòn kết thúc. Brant sẽ &lt;color=Highlight&gt;flips backward&lt;/color&gt; sau &lt;color=Highlight&gt;Mid-air Attack Stage 3&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau mỗi lần &lt;color=Highlight&gt;flip&lt;/color&gt; để thực hiện giai đoạn tiếp theo của &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt;. &lt;color=Highlight&gt;Flip&lt;/color&gt; sẽ đặt lại số lần Tránh Giữa Không.
 - Nếu Brant không tiếp cận được mục tiêu bằng Grapple ở &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt;, cậu sẽ thay thế bằng một nhát chém về phía trước, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 - Nếu Brant tiếp cận được mục tiêu bằng Grapple ở &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt; hoặc &lt;color=Highlight&gt;Stage 2&lt;/color&gt; nhưng đòn đánh không trúng mục tiêu, cậu sẽ rơi xuống sau khi treo lơ lửng một lúc trên không.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13094,10 +13094,10 @@
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Rhapsodic Riff&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-- Giữ Normal Attack sau &lt;color=Highlight&gt;Stage 2&lt;/color&gt; hoặc &lt;color=Highlight&gt;Stage 4&lt;/color&gt; của Basic Attack hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau &lt;color=Highlight&gt;Stage 4&lt;/color&gt; của Mid-air Attack để thực hiện.
+- Giữ Normal Attack sau &lt;color=Highlight&gt;Stage 2&lt;/color&gt; hoặc &lt;color=Highlight&gt;Stage 4&lt;/color&gt; của Basic Attack hoặc {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau &lt;color=Highlight&gt;Stage 4&lt;/color&gt; của Mid-air Attack để thực hiện.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trong &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt; hoặc &lt;color=Highlight&gt;Stage 2&lt;/color&gt; của Mid-air Attack để tấn công mục tiêu hoặc giữ nút để tấn công liên tục. Sau mỗi trong ba &lt;color=Highlight&gt;Flip backward&lt;/color&gt; đầu tiên, nhân vật sẽ tự động &lt;color=Highlight&gt;Mid-air Attack Stages&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau mỗi lần &lt;color=Highlight&gt;flip&lt;/color&gt; để thực hiện giai đoạn tiếp theo của &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt;.
+Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack trong &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt; hoặc &lt;color=Highlight&gt;Stage 2&lt;/color&gt; của Mid-air Attack để tấn công mục tiêu hoặc giữ nút để tấn công liên tục. Sau mỗi trong ba &lt;color=Highlight&gt;Flip backward&lt;/color&gt; đầu tiên, nhân vật sẽ tự động &lt;color=Highlight&gt;Mid-air Attack Stages&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau mỗi lần &lt;color=Highlight&gt;flip&lt;/color&gt; để thực hiện giai đoạn tiếp theo của &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt;.
 Nếu &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt; trượt mục tiêu, nhân vật sẽ lao về phía trước, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
@@ -14257,7 +14257,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -14387,7 +14387,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -14517,7 +14517,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -14647,7 +14647,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Stage 1 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Sát Thương Attack Nạp Stage 1 Mid-air Attack</t>
+          <t>Sát Thương Tấn Công Nạp Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Sát Thương Flip Stage 1 Mid-air Attack</t>
+          <t>Sát Thương Lật Người Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Stage 2 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 2 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -14907,7 +14907,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Stage 2 Đòn Mid-air Attack: Sát Thương Đòn Tích Lũy</t>
+          <t>Giai Đoạn 2 Đòn Mid-air Attack: Charged Attack DMG</t>
         </is>
       </c>
     </row>
@@ -14972,7 +14972,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Stage 2 Đòn Mid-air Attack: Sát Thương Flip</t>
+          <t>Giai Đoạn 2 Đòn Mid-air Attack: Flip DMG</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Stage 3 Đòn Mid-air Attack: Sát Thương</t>
+          <t>Giai Đoạn 3 Đòn Mid-air Attack: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Stage 3 Đòn Mid-air Attack: Sát Thương Flip</t>
+          <t>Giai Đoạn 3 Đòn Mid-air Attack: Flip DMG</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Stage 4 Đòn Mid-air Attack: Sát Thương</t>
+          <t>Giai Đoạn 4 Đòn Mid-air Attack: Sát Thương</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Heavy Attack - Khúc Rhapsody Tiêu Hao Thể Lực</t>
+          <t>Heavy Attack - Khúc Rhapsody Tiêu Hao STA</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Tiêu Hao STA Attack Nạp Trên Không</t>
+          <t>Tiêu Hao STA Tấn Công Nạp Trên Không</t>
         </is>
       </c>
     </row>
@@ -15557,7 +15557,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Sát Thương Plunging Attack</t>
+          <t>Sát Thương Tấn Công Đâm Xuống</t>
         </is>
       </c>
     </row>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Tiêu Hao Thể Lực Plunging Attack</t>
+          <t>Tiêu Hao STA Tấn Công Đâm Xuống</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -15882,7 +15882,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>DMG Hồi Sinh Từ Tro Tàn</t>
+          <t>DMG từ Ashes</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Hồi Phục Sóng Ca Ngợi</t>
+          <t>Sóng Phục Hồi Danh Vọng</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Khiên</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -16207,7 +16207,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Thời Gian Aflame</t>
+          <t>Thời Gian Bốc Cháy</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16272,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>{0}*mỗi 1% Energy Regen</t>
+          <t>{0}*mỗi 1% Hồi Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -16662,7 +16662,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>{0}*mỗi 1% Energy Regen</t>
+          <t>{0}*mỗi 1% Hồi Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>{0}*mỗi 1% Energy Regen</t>
+          <t>{0}*mỗi 1% Hồi Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -17221,7 +17221,7 @@
 Tiêu hao STA để thực hiện Đòn Hạ Gục, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17838,7 +17838,7 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Ripple&lt;/color&gt;&lt;/size&gt;
 Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để bắt đầu chuỗi Basic Attack từ &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để bắt đầu chuỗi Basic Attack từ &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Tidal Surge&lt;/color&gt;&lt;/size&gt;
 Khi ở trạng thái &lt;color=Highlight&gt;Mirage&lt;/color&gt;, &lt;color=Highlight&gt;Intro Skill&lt;/color&gt; sẽ trở thành &lt;color=Highlight&gt;Tidal Surge&lt;/color&gt;, kích hoạt 3 đòn tấn công phối hợp khi trúng mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Sử dụng &lt;color=Highlight&gt;Tidal Surge&lt;/color&gt; sẽ đặt lại chuỗi của &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; trong Basic Attack.</t>
@@ -18014,8 +18014,8 @@
 - &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt;. Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Có thể sử dụng khi đang bay. Khi thi triển trên không, &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; sẽ tiêu hao STA và chuỗi đòn không bị reset khi Cantarella ở trên không.
 - Khi trúng mục tiêu bằng &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt;, tiêu hao {0} điểm Trance để nhận {1} điểm Shiver và hồi phục HP cho tất cả Resonators trong đội ở gần.
 - Đòn thứ ba của &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; kích hoạt 3 đòn Attack Phối Hợp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-- &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thực hiện Đòn Lao Xuống với chi phí STA, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-- &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Shadowy Sweep&lt;/color&gt;. Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng để thực hiện &lt;color=Highlight&gt;Phantom Sting Stage 2&lt;/color&gt;.
+- &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thực hiện Đòn Lao Xuống với chi phí STA, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+- &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Shadowy Sweep&lt;/color&gt;. Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng để thực hiện &lt;color=Highlight&gt;Phantom Sting Stage 2&lt;/color&gt;.
 - Khi &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt; hoặc &lt;color=Highlight&gt;Shadowy Sweep&lt;/color&gt; trúng mục tiêu, tiêu hao {0} điểm Trance để nhận {1} điểm Shiver và hồi phục HP cho tất cả Resonators trong đội ở gần.
 - Mirage kéo dài trong {2} giây.
 - &lt;color=Highlight&gt;Mirage&lt;/color&gt; kết thúc khi Trance cạn kiệt.
@@ -18136,7 +18136,7 @@
           <t>&lt;size=40&gt;&lt;color=Title&gt;Mirage&lt;/color&gt;&lt;/size&gt;
 - &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; - Basic Attack. Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
 - Khi đánh trúng mục tiêu bằng &lt;color=Highlight&gt;Phantom Sting&lt;/color&gt; - Basic Attack, tiêu hao {0} điểm Trance để nhận {1} điểm Shiver và hồi phục HP cho tất cả Resonators trong đội ở gần.
-- &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và tiêu hao STA.
+- &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và tiêu hao STA.
 - &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; chuyển thành &lt;color=Highlight&gt;Shadowy Sweep&lt;/color&gt; - Dodge Counter, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
 - Khi &lt;color=Highlight&gt;Abysmal Vortex&lt;/color&gt; - Mid-air Attack hoặc &lt;color=Highlight&gt;Shadowy Sweep&lt;/color&gt; - Dodge Counter trúng mục tiêu, tiêu hao {0} điểm Trance để nhận {1} điểm Shiver và hồi phục HP cho tất cả Resonators trong đội ở gần.
 - &lt;color=Highlight&gt;Mirage&lt;/color&gt; kết thúc khi Trance cạn kiệt.
@@ -18441,18 +18441,18 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt; trực tiếp.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt; trực tiếp.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Razor Wind&lt;/color&gt;&lt;/size&gt;
 Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; hoặc &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để thi triển Heavy Attack &lt;color=Highlight&gt;Razor Wind&lt;/color&gt;. Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi tiếp đất để thi triển &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;.
-- Khi &lt;te href=850056&gt;Windstrings&lt;/te&gt; đạt tối đa, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi tiếp đất để thi triển Resonance Skill &lt;color=Highlight&gt;Unbound Flow&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi tiếp đất để thi triển &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;.
+- Khi &lt;te href=850056&gt;Windstrings&lt;/te&gt; đạt tối đa, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi tiếp đất để thi triển Resonance Skill &lt;color=Highlight&gt;Unbound Flow&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19295,9 +19295,9 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack - Cloudburst Dance&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 2 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; (được tính là Sát Thương Resonance Skill) và hồi phục HP cho tất cả Resonators trong đội ở gần. Có thể kích hoạt theo 3 cách sau:
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng Resonance Skill &lt;color=Highlight&gt;Awakening Gale&lt;/color&gt;.
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;.
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng Heavy Attack &lt;color=Highlight&gt;Razor Wind&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng Resonance Skill &lt;color=Highlight&gt;Awakening Gale&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng Heavy Attack &lt;color=Highlight&gt;Razor Wind&lt;/color&gt;.
 Khi kích hoạt Mid-air Attack &lt;color=Highlight&gt;Cloudburst Dance&lt;/color&gt;, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Unbound Flow&lt;/color&gt;&lt;/size&gt;
@@ -19657,13 +19657,13 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.
-Sau khi thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; đúng thời điểm để thực hiện Basic Attack &lt;color=Highlight&gt;Breakthrough&lt;/color&gt;, sau đó có thể tiếp tục &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack lần nữa.
+Sau khi thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;, {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; đúng thời điểm để thực hiện Basic Attack &lt;color=Highlight&gt;Breakthrough&lt;/color&gt;, sau đó có thể tiếp tục &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} Normal Attack lần nữa.
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack&lt;/color&gt;&lt;/size&gt;
-Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
-Tiêu hao STA để thực hiện một đòn tấn công lao xuống, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+Tiêu hao STA để thực hiện một đòn tấn công lao xuống, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Sau đó {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; đúng thời điểm để thực hiện Basic Attack &lt;color=Highlight&gt;Breakthrough&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;. Sau đó {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; đúng thời điểm để thực hiện Basic Attack &lt;color=Highlight&gt;Breakthrough&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
       <c r="M265" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Tiêu Chuẩn Defense Protocol&lt;/color&gt;&lt;/size&gt;
-Tấn công mục tiêu để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và chuyển sang tư thế phòng thủ. Trạng thái này sẽ kết thúc sớm nếu Zani rời khỏi chiến trường. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;, hồi 10 điểm &lt;te href=850063&gt;Redundant Energy&lt;/te&gt; và gây Trì Hoãn cho mục tiêu khi trúng đòn.
+Tấn công mục tiêu để gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và chuyển sang tư thế phòng thủ. Trạng thái này sẽ kết thúc sớm nếu Zani rời khỏi chiến trường. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;, hồi 10 điểm &lt;te href=850063&gt;Redundant Energy&lt;/te&gt; và gây Trì Hoãn cho mục tiêu khi trúng đòn.
 Khi bị tấn công trong tư thế phòng thủ, giảm 100% sát thương nhận vào và gây Trì Hoãn cho các mục tiêu xung quanh, sau đó tung ra &lt;color=Highlight&gt;Pinpoint Strike&lt;/color&gt;, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; và giảm thêm &lt;te href=850062&gt;Vibration Strength&lt;/te&gt; của chúng đi {0}. Sát thương Zani phải chịu sẽ giảm {3} trong {2} giây tiếp theo.
 &lt;size=40&gt;&lt;color=Title&gt;Crisis Response Protocol&lt;/color&gt;&lt;/size&gt;
 Khi Zani không ở &lt;color=Highlight&gt;&lt;te href=850064&gt;Inferno Mode&lt;/te&gt;&lt;/color&gt; và có đầy &lt;te href=850063&gt;Redundant Energy&lt;/te&gt;, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của cô sẽ được thay thế bằng Resonance Skill &lt;color=Highlight&gt;Crisis Response Protocol&lt;/color&gt;.
@@ -20656,7 +20656,7 @@
 Tăng sát thương Outro Skill. Số lượng lớp sẽ được tính vào hiệu ứng Sonata Eternal Radiance.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Slash&lt;/color&gt;&lt;/size&gt;
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để sử dụng.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để sử dụng.
 - Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để &lt;color=Highlight&gt;tích lực&lt;/color&gt;, trong quá trình này Zani miễn nhiễm với gián đoạn và có thể chặn đòn tấn công. Chặn thành công sẽ giảm sát thương nhận vào và kích hoạt phản đòn. Thả nút sớm hoặc &lt;color=Highlight&gt;tích lực&lt;/color&gt; để tấn công mục tiêu trực tiếp.
 - Gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;, được tính là cả &lt;color=Highlight&gt;Heavy Attak DMG&lt;/color&gt; và &lt;color=Highlight&gt;Spectro Frazzle DMG&lt;/color&gt;.</t>
         </is>
@@ -21008,7 +21008,7 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. Basic Attack giai đoạn 4 gây 1 tầng &lt;color=Highlight&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; lên mục tiêu trúng đòn.
-- Khi ba giai đoạn đầu của Basic Attack của Ciaccona bị gián đoạn do Dodge, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Basic Attack kịp thời để tiếp tục chu kỳ tấn công và thực hiện giai đoạn Basic Attack tương ứng.
+- Khi ba giai đoạn đầu của Basic Attack của Ciaccona bị gián đoạn do Dodge, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Basic Attack kịp thời để tiếp tục chu kỳ tấn công và thực hiện giai đoạn Basic Attack tương ứng.
 - Sau Basic Attack giai đoạn 4, Ciaccona bắt đầu &lt;color=Highlight&gt;Solo Concert&lt;/color&gt;. Nếu Basic Attack giai đoạn 4 hoặc &lt;color=Highlight&gt;Solo Concert&lt;/color&gt; của Ciaccona kết thúc sớm (chủ động hoặc bị gián đoạn), một &lt;color=Highlight&gt;Ensemble Sylph&lt;/color&gt; sẽ được tạo ra.
 &lt;size=40&gt;&lt;color=Title&gt;Solo Concert&lt;/color&gt;&lt;/size&gt;
 Khi Ciaccona hoặc Ensemble Sylph thực hiện Solo Concert, họ sẽ tăng 24% Aero DMG Bonus cho tất cả Resonators gần đó trong đội. Hiệu ứng này không thể cộng dồn.
@@ -21020,10 +21020,10 @@
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để nhảy lên không trung và tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Aimed Attack&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Aim để vào chế độ Aiming và bắn phát đạn đã tích năng, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là DMG của Heavy Attack.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Aim để vào chế độ Aiming và bắn phát đạn đã tích năng, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là DMG của Heavy Attack.
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện tối đa 2 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau giai đoạn 2 của Mid-air Attack để thực hiện Basic Attack giai đoạn 4.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau giai đoạn 2 của Mid-air Attack để thực hiện Basic Attack giai đoạn 4.
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
 Thực hiện &lt;color=Highlight&gt;Dodges&lt;/color&gt; sau khi &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
         </is>
@@ -21195,7 +21195,7 @@
       <c r="M283" t="inlineStr">
         <is>
           <t>Di chuyển một khoảng nhất định, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và áp 1 tầng &lt;color=Highlight&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; lên mục tiêu khi trúng.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack đúng lúc để thi triển Stage 2 Basic Attack.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack đúng lúc để thi triển Stage 2 Basic Attack.
 - Khi Ciaccona ngắt Normal Attack, Heavy Attack, Đòn Mid-air Attack hoặc &lt;color=Highlight&gt;&lt;te href=850060&gt;Solo Concert&lt;/te&gt;&lt;/color&gt; bằng Resonance Skill, một &lt;color=Highlight&gt;&lt;te href=850059&gt;Ensemble Sylph&lt;/te&gt;&lt;/color&gt; sẽ được tạo ra.
 - Resonance Skill của Ciaccona có thể thi triển giữa không trung.</t>
         </is>
@@ -21341,11 +21341,11 @@
         <is>
           <t>Ciaccona và &lt;color=Highlight&gt;&lt;te href=850059&gt;Ensemble Sylphs&lt;/te&gt;&lt;/color&gt; cùng trình diễn một &lt;color=Highlight&gt;Improvised Symphonic Poem&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; một lần lên các mục tiêu xung quanh và bước vào trạng thái &lt;color=Highlight&gt;Recital&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Recital&lt;/color&gt;&lt;/size&gt;
-Khi ở trạng thái Diễn Tấu, sóng âm sẽ định kỳ tỏa ra xung quanh Ciaccona. Khi sóng âm chồng lên vòng chỉ thị, {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút xanh lá hoặc vàng để tạo ra &lt;color=Highlight&gt;Symphonic Poem: Tonic&lt;/color&gt; tương ứng và hồi một lượng Concerto Energy nhất định.
+Khi ở trạng thái Diễn Tấu, sóng âm sẽ định kỳ tỏa ra xung quanh Ciaccona. Khi sóng âm chồng lên vòng chỉ thị, {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} nút xanh lá hoặc vàng để tạo ra &lt;color=Highlight&gt;Symphonic Poem: Tonic&lt;/color&gt; tương ứng và hồi một lượng Concerto Energy nhất định.
 Trong trạng thái Diễn Tấu:
 - Chuyển sang Resonator khác không kết thúc Diễn Tấu, nhưng sẽ tự động tạo ra một &lt;color=Highlight&gt;Symphonic Poem: Tonic&lt;/color&gt; cùng màu với Âm Chủ cuối cùng được tạo trước khi chuyển. Một &lt;color=Highlight&gt;Symphonic Poem: Tonic&lt;/color&gt; màu xanh lá sẽ được tạo mặc định nếu không có tương tác nào trước khi chuyển sang Resonator khác.
 - Ciaccona miễn nhiễm với gián đoạn và chịu ít hơn {0} Sát Thương.
-- Exit khỏi Diễn Tấu bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} Kỹ Năng Resonance Liberation một lần nữa hoặc đưa Ciaccona trở lại chiến trường.
+- Exit khỏi Diễn Tấu bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} Kỹ Năng Resonance Liberation một lần nữa hoặc đưa Ciaccona trở lại chiến trường.
 - &lt;color=Highlight&gt;&lt;te href=850059&gt;Ensemble Sylphs&lt;/te&gt;&lt;/color&gt; giờ đây có thể trực tiếp tăng Hiệu Quả Aero DMG từ &lt;color=Highlight&gt;&lt;te href=850060&gt;Solo Concert&lt;/te&gt;&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Symphonic Poem: Tonic&lt;/color&gt;&lt;/size&gt;
 Âm Chủ Xanh Lá: Gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên các mục tiêu xung quanh và áp đặt một tầng &lt;color=Highlight&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; lên mục tiêu trúng đòn.
@@ -21426,7 +21426,7 @@
 Gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và bước vào &lt;color=Highlight&gt;Trạng Thái Tăng Cường&lt;/color&gt;.
 &lt;size=10&gt; &lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Trạng Thái Tăng Cường&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} nút tương tác đúng thời điểm để gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và kích hoạt hiệu ứng khác nhau dựa trên màu nút đã bấm:
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút tương tác đúng thời điểm để gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và kích hoạt hiệu ứng khác nhau dựa trên màu nút đã bấm:
 - Xanh lá: Gây &lt;color=Highlight&gt;Erosion Aero&lt;/color&gt;.
 - Vàng: Gây &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt;.
 Ciaccona sẽ duy trì &lt;color=Highlight&gt;Trạng Thái Tăng Cường&lt;/color&gt; sau khi chuyển sang Resonators khác, và kích hoạt lại hiệu ứng của nút cuối cùng đã bấm trước khi chuyển.
@@ -22257,10 +22257,10 @@
 Lượng sát thương này được tính là &lt;color=Highlight&gt;Basic Attack DMG&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack - Cartethyia&lt;/color&gt;&lt;/size&gt;
 Thả nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; khi đang ở trên không để thực hiện Đòn Lao Xuống với chi phí STA, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, cũng được tính là sát thương &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau &lt;color=Highlight&gt;Plunging Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Cartethyia Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau &lt;color=Highlight&gt;Plunging Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Cartethyia Stage 2&lt;/color&gt;.
 Sử dụng &lt;color=Highlight&gt;Mid-air Attack - Cartethyia&lt;/color&gt; sẽ thu hồi tất cả &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt;. Tùy theo loại và số lượng &lt;color=Highlight&gt;Kiếm Shadows&lt;/color&gt; thu hồi, thực hiện các hình thức Đòn Lao Xuống khác nhau và nhận được &lt;color=Highlight&gt;&lt;te href=850181&gt;Heart of Virtue&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;&lt;te href=850182&gt;Mandate of Divinity&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=850183&gt;Power of Discord&lt;/te&gt;&lt;/color&gt; tương ứng.
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Cartethyia&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23033,10 +23033,10 @@
           <t>&lt;size=40&gt;&lt;color=Title&gt;Cartethyia - Kiếm to Mark Tide's Trace&lt;/color&gt;&lt;/size&gt;
 Gây Aero DMG và áp 2 lớp &lt;color=Wind&gt;&lt;te href=850009&gt;Aero Erosion&lt;/te&gt;&lt;/color&gt; lên mục tiêu trúng đòn. Summon &lt;color=Highlight&gt;&lt;te href=850185&gt;Kiếm of Discord's Shadow&lt;/te&gt;&lt;/color&gt;.
 Tối đa 1 &lt;color=Highlight&gt;&lt;te href=850185&gt;Kiếm of Discord's Shadow&lt;/te&gt;&lt;/color&gt; có thể tồn tại cùng lúc, kéo dài 20 giây.
-{Cus:Ipt,Touch=Tấn PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau &lt;color=Highlight&gt;Cartethyia - Kiếm to Mark Tide's Trace&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Cartethyia Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau &lt;color=Highlight&gt;Cartethyia - Kiếm to Mark Tide's Trace&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Cartethyia Stage 2&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Fleurdelys - Kiếm to Call for Freedom&lt;/color&gt;&lt;/size&gt;
 Đâm thẳng về phía trước để xuyên thủng mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt;.
-{Cus:Ipt,Touch=Tấn PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau &lt;color=Highlight&gt;Fleurdelys - Kiếm to Call for Freedom&lt;/color&gt; để tung chiêu &lt;color=Highlight&gt;Basic Attack - Fleurdelys Stage 2&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau &lt;color=Highlight&gt;Fleurdelys - Kiếm to Call for Freedom&lt;/color&gt; để tung chiêu &lt;color=Highlight&gt;Basic Attack - Fleurdelys Stage 2&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23218,22 +23218,22 @@
 &lt;color=Highlight&gt;Heavy Attack - Cartethyia&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Heavy Attack - Fleurdelys&lt;/color&gt;.
 Đâm về phía trước để tung ra một đòn tấn công tập trung, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt; khi trúng đích. Lượng sát thương này được tính là Sát Thương Basic Attack.
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack Cường Hóa - Fleurdelys&lt;/color&gt;&lt;/size&gt;
-Trong khi thi triển &lt;color=Highlight&gt;Heavy Attack - Fleurdelys&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; một lần nữa để thi triển &lt;color=Highlight&gt;Heavy Attack Cường Hóa - Fleurdelys&lt;/color&gt;: lùi lại và bắn một luồng năng lượng thẳng về phía trước, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt; khi trúng đích. Lượng sát thương này được tính là Sát Thương Basic Attack.
+Trong khi thi triển &lt;color=Highlight&gt;Heavy Attack - Fleurdelys&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; một lần nữa để thi triển &lt;color=Highlight&gt;Heavy Attack Cường Hóa - Fleurdelys&lt;/color&gt;: lùi lại và bắn một luồng năng lượng thẳng về phía trước, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt; khi trúng đích. Lượng sát thương này được tính là Sát Thương Basic Attack.
 Ngay sau khi thi triển &lt;color=Highlight&gt;Heavy Attack Cường Hóa - Fleurdelys&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Đòn Chém Lên - Fleurdelys&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Đòn Chém Lên - Fleurdelys&lt;/color&gt;&lt;/size&gt;
 Khi &lt;color=Highlight&gt;Fleurdelys&lt;/color&gt; đang ở trên mặt đất, &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thi triển kỹ năng này, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt; khi trúng đích.
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Fleurdelys&lt;/color&gt;&lt;/size&gt; 
 &lt;color=Highlight&gt;Dodge Counter - Cartethyia&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Dodge Counter - Fleurdelys&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt; khi trúng đích.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt; khi trúng đích.
 Ngay sau đó, sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Basic Attack - Fleurdelys Stage 4&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Kiếm Đáp Lời Sóng Gió&lt;/color&gt;&lt;/size&gt; 
 &lt;color=Highlight&gt;Resonance Skill - Cartethyia&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Resonance Skill - Kiếm Đáp Lời Sóng Gió&lt;/color&gt;.
 Summon một trường lực gần vị trí mục tiêu để liên tục hút các mục tiêu xung quanh, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt; khi trúng đích.
 Có thể thi triển trên không.
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Tempest Phá Tan Triều Dâng&lt;/color&gt;&lt;/size&gt;
-Sau khi thi triển &lt;color=Highlight&gt;Resonance Skill - Kiếm Đáp Lời Sóng Gió&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; một lần nữa để gọi xuống một Bóng Kiếm khổng lồ đè nát khu vực xung quanh mục tiêu, tạo ra trường lực hút các mục tiêu gần đó, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên mục tiêu trên mặt đất và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt; khi trúng đích.
+Sau khi thi triển &lt;color=Highlight&gt;Resonance Skill - Kiếm Đáp Lời Sóng Gió&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; một lần nữa để gọi xuống một Bóng Kiếm khổng lồ đè nát khu vực xung quanh mục tiêu, tạo ra trường lực hút các mục tiêu gần đó, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; lên mục tiêu trên mặt đất và hồi phục &lt;color=Highlight&gt;&lt;te href=850179&gt;Conviction&lt;/te&gt;&lt;/color&gt; khi trúng đích.
 Ngay sau đó, sử dụng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Basic Attack - Fleurdelys Stage 3&lt;/color&gt;.
-Resonance Skill sẽ bước vào Cooldown chiêu nếu &lt;color=Highlight&gt;Resonance Skill - Tempest Phá Tan Triều Dâng&lt;/color&gt; không được thi triển trong một khoảng thời gian nhất định hoặc khi chuyển sang Resonator khác.
+Resonance Skill sẽ bước vào Thời gian hồi chiêu nếu &lt;color=Highlight&gt;Resonance Skill - Tempest Phá Tan Triều Dâng&lt;/color&gt; không được thi triển trong một khoảng thời gian nhất định hoặc khi chuyển sang Resonator khác.
 Có thể thi triển trên không.</t>
         </is>
       </c>
@@ -23597,8 +23597,8 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-- Sau Basic Attack Stage 3, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack đúng thời điểm để thực hiện &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt;.
-- Sau &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt;, Basic Attack &lt;color=Highlight&gt;Starfall&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Shewolf's Hunt&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Feral Fang&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack đúng thời điểm để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
+- Sau Basic Attack Stage 3, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack đúng thời điểm để thực hiện &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt;.
+- Sau &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt;, Basic Attack &lt;color=Highlight&gt;Starfall&lt;/color&gt;, Resonance Skill &lt;color=Highlight&gt;Shewolf's Hunt&lt;/color&gt; hoặc Resonance Skill &lt;color=Highlight&gt;Feral Fang&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack đúng thời điểm để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Wolf's Gnawing&lt;/color&gt;&lt;/size&gt;
@@ -23606,7 +23606,7 @@
 - Đòn tấn công này không phục hồi &lt;te href=850174&gt;Wolflame&lt;/te&gt;. Tiêu hao {1} điểm &lt;te href=850174&gt;Wolflame&lt;/te&gt; để thực hiện đòn tấn công này và nhận &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=point P=points SapTag=2} &lt;te href=850175&gt;Wolfaith&lt;/te&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Wolf's Claw&lt;/color&gt;&lt;/size&gt;
 Khi &lt;te href=850174&gt;Wolflame&lt;/te&gt; đạt {3} điểm và &lt;te href=850175&gt;Wolfaith&lt;/te&gt; đạt {4} điểm, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Wolf's Claw&lt;/color&gt;, tiêu hao STA để tấn công mục tiêu và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-- Nếu &lt;te href=850174&gt;Wolflame&lt;/te&gt; đạt {5} điểm và &lt;te href=850175&gt;Wolfaith&lt;/te&gt; đạt {6} điểm sau khi thực hiện &lt;color=Highlight&gt;Mid-air Attack - Firestrike&lt;/color&gt; hoặc &lt;color=Highlight&gt;Heavy Attack - Wolf's Gnawing&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; đúng thời điểm để thực hiện &lt;color=Highlight&gt;Heavy Attack - Wolf's Claw&lt;/color&gt;.
+- Nếu &lt;te href=850174&gt;Wolflame&lt;/te&gt; đạt {5} điểm và &lt;te href=850175&gt;Wolfaith&lt;/te&gt; đạt {6} điểm sau khi thực hiện &lt;color=Highlight&gt;Mid-air Attack - Firestrike&lt;/color&gt; hoặc &lt;color=Highlight&gt;Heavy Attack - Wolf's Gnawing&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; đúng thời điểm để thực hiện &lt;color=Highlight&gt;Heavy Attack - Wolf's Claw&lt;/color&gt;.
 - Đòn tấn công này không phục hồi &lt;te href=850174&gt;Wolflame&lt;/te&gt;. Tiêu hao {7} điểm &lt;te href=850174&gt;Wolflame&lt;/te&gt; để thực hiện đòn tấn công này và nhận &lt;SapTag=8&gt;{8}&lt;/SapTag&gt; {Cus:Sap,S=point P=points SapTag=8} &lt;te href=850175&gt;Wolfaith&lt;/te&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện tối đa 3 đòn tấn công trên không, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Chu kỳ &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; sẽ không được đặt lại.
@@ -23614,12 +23614,12 @@
 Khi &lt;te href=850174&gt;Wolflame&lt;/te&gt; đạt {9} điểm, &lt;color=Highlight&gt;Mid-air Attack Stage 3&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Mid-air Attack - Firestrike&lt;/color&gt;, tiêu hao STA để tấn công mục tiêu và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; (được tính là DMG của Heavy Attack).
 - Đòn tấn công này không phục hồi &lt;te href=850174&gt;Wolflame&lt;/te&gt;. Tiêu hao {10} điểm &lt;te href=850174&gt;Wolflame&lt;/te&gt; để thực hiện đòn tấn công này và nhận &lt;SapTag=11&gt;{11}&lt;/SapTag&gt; {Cus:Sap,S=point P=points SapTag=11} &lt;te href=850175&gt;Wolfaith&lt;/te&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Plunging Attack&lt;/color&gt;&lt;/size&gt;
-Giữ Normal Attack khi đang trên không để thực hiện Plunging Attack với chi phí STA, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Sau khi thực hiện đòn tấn công này, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack đúng thời điểm để thực hiện Basic Attack &lt;color=Highlight&gt;Starfall&lt;/color&gt;.
-- Nếu thực hiện &lt;color=Highlight&gt;Dodge&lt;/color&gt; trong khi đang thực hiện &lt;color=Highlight&gt;Mid-air Attack Stage 3&lt;/color&gt; hoặc &lt;color=Highlight&gt;Mid-air Attack - Firestrike&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Plunging Attack&lt;/color&gt; đúng thời điểm với chi phí STA.
+Giữ Normal Attack khi đang trên không để thực hiện Plunging Attack với chi phí STA, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Sau khi thực hiện đòn tấn công này, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack đúng thời điểm để thực hiện Basic Attack &lt;color=Highlight&gt;Starfall&lt;/color&gt;.
+- Nếu thực hiện &lt;color=Highlight&gt;Dodge&lt;/color&gt; trong khi đang thực hiện &lt;color=Highlight&gt;Mid-air Attack Stage 3&lt;/color&gt; hoặc &lt;color=Highlight&gt;Mid-air Attack - Firestrike&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Plunging Attack&lt;/color&gt; đúng thời điểm với chi phí STA.
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Starfall&lt;/color&gt;&lt;/size&gt;
 Tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -23796,7 +23796,7 @@
 Có thể thực hiện khi đang ở gần mặt đất trên không.
 - Giữ Resonance Skill để bật lên không trung, sau đó {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; đúng lúc để tung &lt;color=Highlight&gt;Mid-air Attack Stage 1&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Feral Fang&lt;/color&gt;&lt;/size&gt;
-Lupa khóa mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi {2} điểm &lt;te href=850174&gt;Wolflame&lt;/te&gt;. Hệ số Sát Thương đối với mục tiêu &lt;color=Highlight&gt;marked&lt;/color&gt; tăng {3}. Resonance Skill - Nanh Dã Thú sẽ进入 Cooldown nếu không được kích hoạt kịp thời hoặc khi Lupa bị thay ra.</t>
+Lupa khóa mụcaim mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi {2} điểm &lt;te href=850174&gt;Wolflame&lt;/te&gt;. Hệ số Sát Thương đối với mục tiêu &lt;color=Highlight&gt;marked&lt;/color&gt; tăng {3}. Resonance Skill - Nanh Dã Thú sẽ bắt đầu Thời gian hồi nếu không được kích hoạt kịp thời hoặc khi Lupa bị thay ra.</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24034,7 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Resonance Liberation&lt;/color&gt;&lt;/size&gt;
 Tất cả Resonators trong đội nhận &lt;color=Highlight&gt;Pack Hunt&lt;/color&gt;. Tiêu hao toàn bộ &lt;color=Highlight&gt;&lt;te href=850175&gt;Wolfaith&lt;/te&gt;&lt;/color&gt; để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack hoặc Resonance Skill đúng lúc để thực hiện &lt;color=Highlight&gt;Foebreaker&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack hoặc Resonance Skill đúng lúc để thực hiện &lt;color=Highlight&gt;Foebreaker&lt;/color&gt;.
 Sau khi sử dụng &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;, tất cả Resonators trong đội nhận &lt;color=Highlight&gt;Pack Hunt&lt;/color&gt; và thêm Attack cộng dồn. Nếu Resonators đang hoạt động bị đánh trúng hoặc tung lên không, họ sẽ hồi phục ngay lập tức. Khi Resonators đang hoạt động sử dụng Intro Skill, &lt;color=Highlight&gt;Pack Hunt&lt;/color&gt; được tăng cường, cung cấp thêm Attack cộng dồn, tối đa 2 lần. Khi Resonators có &lt;color=Highlight&gt;Pack Hunt&lt;/color&gt; tấn công mục tiêu cấp Overlord hoặc Calamity, họ nhận thêm cộng dồn Fusion DMG.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Foebreaker&lt;/color&gt;&lt;/size&gt;
@@ -24243,7 +24243,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Tiêu diệt mục tiêu &lt;color=Highlight&gt;marked&lt;/color&gt; sẽ làm mới Cooldown chiêu của Resonance Skill &lt;color=Highlight&gt;Shewolf's Hunt&lt;/color&gt;.
+          <t>Tiêu diệt mục tiêu &lt;color=Highlight&gt;marked&lt;/color&gt; sẽ làm mới Thời gian hồi chiêu của Resonance Skill &lt;color=Highlight&gt;Shewolf's Hunt&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Liberation - Glory&lt;/color&gt;&lt;/size&gt;
 Kích hoạt Resonance Liberation &lt;color=Highlight&gt;Fire-Kissed Glory&lt;/color&gt; sẽ ban hiệu ứng &lt;color=Highlight&gt;Glory&lt;/color&gt;. Trong vòng {0} giây:
 Các đòn tấn công của tất cả Resonators trong đội sẽ bỏ qua {1} Kháng Hệ của mục tiêu. Với mỗi Resonators Hệ Fusion trong đội ngoài Lupa, hiệu ứng này tăng thêm {2}, tối đa {3}. Khi có {4} Resonators Hệ Fusion trong đội, các đòn tấn công của Resonators sẽ bỏ qua thêm {5} Kháng Hệ Fusion.</t>
@@ -24313,7 +24313,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Tiêu diệt &lt;color=Highlight&gt;marked&lt;/color&gt; sẽ làm mới Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;.
+          <t>Tiêu diệt &lt;color=Highlight&gt;marked&lt;/color&gt; sẽ làm mới Thời gian hồi chiêu của &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;.
 Thực hiện &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; sẽ ban cho tất cả Resonators trong đội &lt;color=Highlight&gt;Glory&lt;/color&gt;:
 Các đòn tấn công của họ sẽ xuyên qua một lượng Fusion RES nhất định. Hiệu ứng tăng cường nếu đội có nhiều Resonators Fusion hơn.</t>
         </is>
@@ -24382,7 +24382,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau Intro Skill &lt;color=Highlight&gt;Try Focusing, Eh?&lt;/color&gt; để tung &lt;color=Highlight&gt;Mid-air Attack Stage 3&lt;/color&gt;.
+          <t>Tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau Intro Skill &lt;color=Highlight&gt;Try Focusing, Eh?&lt;/color&gt; để tung &lt;color=Highlight&gt;Mid-air Attack Stage 3&lt;/color&gt;.
 &lt;size=40&gt;&lt;color=Title&gt;Nowhere to Run!&lt;/color&gt;&lt;/size&gt;
 Khi Lupa bước vào trạng thái &lt;color=Highlight&gt;Wild Hunt&lt;/color&gt;, Intro Skill tiếp theo của cô sẽ được thay thế bằng &lt;color=Highlight&gt;Nowhere to Run!&lt;/color&gt;. Sử dụng &lt;color=Highlight&gt;Nowhere to Run!&lt;/color&gt; sẽ loại bỏ hiệu ứng &lt;color=Highlight&gt;&lt;te href=850176&gt;Pack Hunt&lt;/te&gt;&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=850178&gt;Glory&lt;/te&gt;&lt;/color&gt; trên tất cả Resonators trong đội, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; (được tính là Sát Thương Resonance Liberation).</t>
         </is>
@@ -25007,7 +25007,7 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Scarlet Coda&lt;/color&gt;&lt;/size&gt;
 Phrolova bước vào trạng thái &lt;color=Highlight&gt;Compose&lt;/color&gt; mỗi {1} giây.
@@ -25019,14 +25019,14 @@
 &lt;color=Highlight&gt;Scarlet Coda&lt;/color&gt;: Tiêu hao STA để gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;, làm chậm và kéo các mục tiêu gần đó về phía mình. Sát thương này được tính là &lt;color=Highlight&gt;Resonance Skill DMG&lt;/color&gt;.
 Mỗi lớp &lt;color=Highlight&gt;&lt;te href=160803&gt;Aftersound&lt;/te&gt;&lt;/color&gt; sẽ tăng thêm Hệ Số Sát Thương của lần gây sát thương này.
 Sử dụng kỹ năng này được tính là sử dụng &lt;color=Highlight&gt;Echo Skill&lt;/color&gt;.
-Sử dụng kỹ năng này sẽ đưa trạng thái &lt;color=Highlight&gt;Compose&lt;/color&gt; vào Cooldown chiêu và kích hoạt trạng thái &lt;color=Highlight&gt;Resolving Chord&lt;/color&gt;.
+Sử dụng kỹ năng này sẽ đưa trạng thái &lt;color=Highlight&gt;Compose&lt;/color&gt; vào Thời gian hồi chiêu và kích hoạt trạng thái &lt;color=Highlight&gt;Resolving Chord&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Đòn Hạ Gục, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -25367,10 +25367,10 @@
 Phrolova lơ lửng trên không và điều khiển Hecate chiến đấu. Hecate sẽ thừa hưởng chỉ số và trạng thái của Phrolova, và sát thương gây ra bởi Hecate sẽ được tính là đến từ Phrolova. Các đòn tấn công của Hecate sẽ không loại bỏ trạng thái Hazy Dream của mục tiêu.
 Trong thời gian này, Phrolova lần lượt chơi các &lt;color=Highlight&gt;&lt;te href=160801&gt;Volatile Notes&lt;/te&gt;&lt;/color&gt;. Mỗi &lt;color=Highlight&gt;Volatile Ghi chú&lt;/color&gt; duy trì trong {1}s.
 Nếu Phrolova là Resonators đang hoạt động trên chiến trường, cô có thể đưa ra các tín hiệu sau cho Hecate. Mọi sát thương Hecate chịu trong trạng thái này cũng sẽ ảnh hưởng đến Phrolova.
-- &lt;color=Highlight&gt;Cue - Basic Attack&lt;/color&gt;: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để ra lệnh cho Hecate sử dụng &lt;color=Highlight&gt;Basic Attack - Hecate&lt;/color&gt;. Khi Phrolova là Resonators đang hoạt động trên chiến trường, cứ mỗi {2} lần Hecate sử dụng &lt;color=Highlight&gt;Basic Attack - Hecate&lt;/color&gt;, đòn &lt;color=Highlight&gt;Basic Attack - Hecate&lt;/color&gt; tiếp theo sẽ được thay thế bằng &lt;color=Highlight&gt;Enhanced Attack - Hecate&lt;/color&gt;.
-- &lt;color=Highlight&gt;Cue - Dodge&lt;/color&gt;: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge để ra lệnh cho Hecate Dodge đòn. Hecate không chịu sát thương từ đòn đánh Dodge thành công.
-- &lt;color=Highlight&gt;Cue - Đặt lại&lt;/color&gt;: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy để đặt lại vị trí của Hecate.
-- &lt;color=Highlight&gt;Cue - Curtain Call&lt;/color&gt;: {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation để ra lệnh cho Hecate sử dụng &lt;color=Highlight&gt;Curtain Call&lt;/color&gt; và kết thúc trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt;.
+- &lt;color=Highlight&gt;Cue - Basic Attack&lt;/color&gt;: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack để ra lệnh cho Hecate sử dụng &lt;color=Highlight&gt;Basic Attack - Hecate&lt;/color&gt;. Khi Phrolova là Resonators đang hoạt động trên chiến trường, cứ mỗi {2} lần Hecate sử dụng &lt;color=Highlight&gt;Basic Attack - Hecate&lt;/color&gt;, đòn &lt;color=Highlight&gt;Basic Attack - Hecate&lt;/color&gt; tiếp theo sẽ được thay thế bằng &lt;color=Highlight&gt;Enhanced Attack - Hecate&lt;/color&gt;.
+- &lt;color=Highlight&gt;Cue - Dodge&lt;/color&gt;: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Dodge để ra lệnh cho Hecate Dodge đòn. Hecate không chịu sát thương từ đòn đánh Dodge thành công.
+- &lt;color=Highlight&gt;Cue - Đặt lại&lt;/color&gt;: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Nhảy để đặt lại vị trí của Hecate.
+- &lt;color=Highlight&gt;Cue - Curtain Call&lt;/color&gt;: {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Liberation để ra lệnh cho Hecate sử dụng &lt;color=Highlight&gt;Curtain Call&lt;/color&gt; và kết thúc trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt;.
 Khi Phrolova không phải là Resonators đang hoạt động, Hecate không chịu sát thương và tự động sử dụng &lt;color=Highlight&gt;Basic Attack - Hecate&lt;/color&gt; để tấn công mục tiêu. Khi Resonators trong đội sử dụng Echoes Skill, Hecate sẽ sử dụng &lt;color=Highlight&gt;Enhanced Attack - Hecate&lt;/color&gt; để tấn công mục tiêu. Hiệu ứng này có thể được kích hoạt tối đa {4} lần trong suốt trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt; của Phrolova. Các Echoes cùng tên có thể kích hoạt hiệu ứng này &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}.
 Switch về Phrolova sẽ kết thúc trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt;.
 End trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt; sẽ loại bỏ tất cả &lt;color=Highlight&gt;Volatile Notes&lt;/color&gt;.
@@ -25392,7 +25392,7 @@
 - Khi Phrolova là Resonators đang hoạt động trên chiến trường, kết thúc trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt;.
 - Khi Phrolova đang ở trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt;, chuyển về Phrolova mà không sử dụng Intro Skill.
 - Khi Phrolova không phải là Resonators đang hoạt động và trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt; kết thúc, chuyển về Phrolova mà không sử dụng Intro Skill.
-- Khi Phrolova đang ở trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation.
+- Khi Phrolova đang ở trạng thái &lt;color=Highlight&gt;Maestro&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Liberation.
 - Khi Phrolova đang ở trạng thái &lt;color=Highlight&gt;Resolving Chord&lt;/color&gt;, giữ Resonance Liberation.
 Khi ở trạng thái &lt;color=Highlight&gt;Resolving Chord&lt;/color&gt;, sử dụng &lt;color=Highlight&gt;Curtain Call&lt;/color&gt; sẽ loại bỏ tất cả &lt;color=Highlight&gt;Volatile Notes&lt;/color&gt; và kết thúc trạng thái &lt;color=Highlight&gt;Resolving Chord&lt;/color&gt;.</t>
         </is>
@@ -25822,11 +25822,11 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Suite of Quietus&lt;/color&gt;&lt;/size&gt;
 Tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Suite of Immortality&lt;/color&gt;&lt;/size&gt;
 Khi ở trạng thái &lt;color=Highlight&gt;&lt;te href=160804&gt;Maestro&lt;/te&gt;&lt;/color&gt;, &lt;color=Highlight&gt;Suite of Quietus&lt;/color&gt; tiếp theo sẽ được thay thế bằng &lt;color=Highlight&gt;Suite of Immortality&lt;/color&gt;. Sự thay thế này sẽ bị hủy nếu &lt;color=Highlight&gt;Curtain Call&lt;/color&gt; được sử dụng trong trạng thái này. &lt;color=Highlight&gt;Suite of Immortality&lt;/color&gt; gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; (được tính là &lt;color=Highlight&gt;Resonance Skill DMG&lt;/color&gt;) và khiến mục tiêu bị Trì Hoãn.
-{Cus:Ipt,Touch=Touch PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung ra &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -26430,14 +26430,14 @@
 Tiêu hao STA để thực hiện Đòn Hạ Gục, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Moonring - Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu bằng &lt;color=Highlight&gt;Moonring&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack một lần nữa ngay sau khi sử dụng kỹ năng này để thực hiện Vòng Trăng - Basic Attack Stage 3.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu bằng &lt;color=Highlight&gt;Moonring&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack một lần nữa ngay sau khi sử dụng kỹ năng này để thực hiện Vòng Trăng - Basic Attack Stage 3.
 &lt;size=40&gt;&lt;color=Title&gt;Moonbow - Basic Attack&lt;/color&gt;&lt;/size&gt;
 Nhập &lt;color=Highlight&gt;&lt;te href=141001&gt;Lunar Cycle&lt;/te&gt;&lt;/color&gt; bằng cách sử dụng &lt;color=Highlight&gt;Heavy Attack - Flux: Moonring&lt;/color&gt;. Khi ở trạng thái này, Iuno sẽ tấn công bằng &lt;color=Highlight&gt;Moonbow&lt;/color&gt;.
 Thực hiện tối đa 3 đòn tấn công liên tiếp bằng &lt;color=Highlight&gt;Moonbow&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
 Có thể sử dụng khi đang ở trên không.
 &lt;size=40&gt;&lt;color=Title&gt;Moonbow - Dodge Counter&lt;/color&gt;&lt;/size&gt;
-Khi ở &lt;color=Highlight&gt;Lunar Cycle - New Moon&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu bằng &lt;color=Highlight&gt;Moonbow&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
-Khi ở &lt;color=Highlight&gt;Lunar Cycle - New Moon&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack một lần nữa ngay sau khi sử dụng kỹ năng này để thực hiện Cung Trăng - Basic Attack Stage 3.
+Khi ở &lt;color=Highlight&gt;Lunar Cycle - New Moon&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu bằng &lt;color=Highlight&gt;Moonbow&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
+Khi ở &lt;color=Highlight&gt;Lunar Cycle - New Moon&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack một lần nữa ngay sau khi sử dụng kỹ năng này để thực hiện Cung Trăng - Basic Attack Stage 3.
 Có thể sử dụng khi đang ở trên không.</t>
         </is>
       </c>
@@ -26613,7 +26613,7 @@
 &lt;size=40&gt;&lt;color=Title&gt;Unfinished Refrain&lt;/color&gt;&lt;/size&gt;
 Khi ở trong &lt;color=Highlight&gt;Lunar Cycle - Half Moon&lt;/color&gt;, Resonance Skill của Iuno sẽ được thay thế bằng &lt;color=Highlight&gt;Unfinished Refrain&lt;/color&gt;.
 Sử dụng Khúc Đoạn Chưa Hoàn Thành tung ra hàng loạt đòn tấn công, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-Khúc Đoạn Chưa Hoàn Thành có chung Cooldown chiêu với Khúc Kết Đoạn.
+Khúc Đoạn Chưa Hoàn Thành có chung Thời gian hồi chiêu với Khúc Kết Đoạn.
 &lt;size=40&gt;&lt;color=Title&gt;Arc Beyond the Edge&lt;/color&gt;&lt;/size&gt;
 Khi Iuno ở trong &lt;color=Highlight&gt;Lunar Cycle - New Moon&lt;/color&gt;, Resonance Skill của cô sẽ được thay thế bằng &lt;color=Highlight&gt;Arc Beyond the Edge&lt;/color&gt;, với 2 lượt sử dụng ban đầu.
 Sử dụng Vòng Cung Vượt Biên khiến Iuno dịch chuyển vị trí và gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Resonance Liberation.
@@ -27872,36 +27872,36 @@
 Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Steelclash&lt;/color&gt;&lt;/size&gt;
-Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;. &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; ngay sau khi thực hiện Heavy Attack để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
+Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;. &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; ngay sau khi thực hiện Heavy Attack để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Đòn Lao Xuống từ giữa không trung, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Dodge Counter&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; sau khi Dodge Giữa Không thành công để thực hiện Đòn Lao Xuống với chi phí STA, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; sau khi Dodge Giữa Không thành công để thực hiện Đòn Lao Xuống với chi phí STA, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Thunderoar: Backstep&lt;/color&gt;&lt;/size&gt;
 Khi &lt;te href=130602&gt;Prowess&lt;/te&gt; đầy, &lt;color=Highlight&gt;Heavy Attack - Steelclash&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Backstep&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Thiên Phú.
-- Trong khi thi triển, &lt;color=Highlight&gt;release&lt;/color&gt; hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; lại trong một khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Spinslash&lt;/color&gt;.
+- Trong khi thi triển, &lt;color=Highlight&gt;release&lt;/color&gt; hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; lại trong một khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Spinslash&lt;/color&gt;.
 - &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Spinslash&lt;/color&gt; có thể sử dụng nếu Augusta vẫn đứng trên mặt đất trong một khoảng thời gian nhất định sau khi kỹ năng này bị gián đoạn.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Thunderoar: Spinslash&lt;/color&gt;&lt;/size&gt;
-Augusta xoay người và vung Lưỡi Broadblade, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
+Augusta xoay người và vung Lưỡi Đại kiếm, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy&lt;/color&gt; khi &lt;te href=130602&gt;Prowess&lt;/te&gt; đầy để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Thiên Phú.
-Nếu Thiên Phú đầy khi thi triển &lt;color=Highlight&gt;Resonance Skill - Warrior's Blade&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Thiên Phú.
-Nếu Thiên Phú đầy khi thi triển &lt;color=Highlight&gt;Heavy Attack - Steelclash&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter – Heavy Attack: Steelclash&lt;/color&gt;, &lt;color=Highlight&gt;release Normal Attack&lt;/color&gt; sau một khoảng thời gian hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; lại để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Thiên Phú.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Nhảy&lt;/color&gt; khi &lt;te href=130602&gt;Prowess&lt;/te&gt; đầy để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Thiên Phú.
+Nếu Thiên Phú đầy khi thi triển &lt;color=Highlight&gt;Resonance Skill - Warrior's Blade&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Thiên Phú.
+Nếu Thiên Phú đầy khi thi triển &lt;color=Highlight&gt;Heavy Attack - Steelclash&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge Counter – Heavy Attack: Steelclash&lt;/color&gt;, &lt;color=Highlight&gt;release Normal Attack&lt;/color&gt; sau một khoảng thời gian hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Nhảy&lt;/color&gt; lại để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Uppercut&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; và tiêu hao toàn bộ Thiên Phú.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Heavy Attack: Steelclash&lt;/color&gt;&lt;/size&gt;
 Khi &lt;te href=130602&gt;Prowess&lt;/te&gt; đầy, &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Dodge Counter - Heavy Attack: Steelclash&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Thunderoar: Backstep&lt;/color&gt;&lt;/size&gt;
-Khi &lt;te href=130603&gt;Ascendancy&lt;/te&gt; đầy, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; sau khi Dodge thành công trên mặt đất để thi triển &lt;color=Highlight&gt;Dodge Counter - Thunderoar: Backstep&lt;/color&gt; thay cho &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter - Heavy Attack: Steelclash&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.
-- &lt;color=Highlight&gt;Release&lt;/color&gt; hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack&lt;/color&gt; lại trong một khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Spinslash&lt;/color&gt;.
+Khi &lt;te href=130603&gt;Ascendancy&lt;/te&gt; đầy, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; sau khi Dodge thành công trên mặt đất để thi triển &lt;color=Highlight&gt;Dodge Counter - Thunderoar: Backstep&lt;/color&gt; thay cho &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; và &lt;color=Highlight&gt;Dodge Counter - Heavy Attack: Steelclash&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.
+- &lt;color=Highlight&gt;Release&lt;/color&gt; hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack&lt;/color&gt; lại trong một khoảng thời gian nhất định để thực hiện &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Spinslash&lt;/color&gt;.
 - &lt;color=Highlight&gt;Heavy Attack - Thunderoar: Spinslash&lt;/color&gt; có thể sử dụng nếu Augusta vẫn đứng trên mặt đất trong một khoảng thời gian nhất định sau khi kỹ năng này bị gián đoạn.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Prowess&lt;/color&gt;&lt;/size&gt;
@@ -28051,7 +28051,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Augusta nhảy lên rồi đập mạnh Lưỡi Broadblade xuống, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
+          <t>Augusta nhảy lên rồi đập mạnh Lưỡi Đại kiếm xuống, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -28206,16 +28206,16 @@
       <c r="M374" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Resonance Liberation - Kiếm of Eternal Oath&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} và thả Resonance Liberation&lt;/color&gt; để thi triển kỹ năng. Augusta sẽ vung Lưỡi Broadblade về phía trước, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} và thả Resonance Liberation&lt;/color&gt; để thi triển kỹ năng. Augusta sẽ vung Lưỡi Đại kiếm về phía trước, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Liberation - Sublime is the Sun&lt;/color&gt;&lt;/size&gt;
 Khi &lt;te href=130604&gt;Majesty&lt;/te&gt; đạt {0} tầng, &lt;color=Highlight&gt;giữ Resonance Liberation&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Resonance Liberation - Sublime is the Sun&lt;/color&gt;. Việc thi triển &lt;color=Highlight&gt;Resonance Liberation - Sublime is the Sun&lt;/color&gt; không tốn Resonance Energy mà thay vào đó là {0} tầng Oai Phong.
 - Khi thi triển &lt;color=Highlight&gt;Resonance Liberation - Sublime is the Sun&lt;/color&gt;, Augusta tạo ra &lt;color=Highlight&gt;&lt;te href=130605&gt;Ruler's Realm&lt;/te&gt;&lt;/color&gt; và bước vào trạng thái &lt;color=Highlight&gt;&lt;te href=130606&gt;Sworn Allegiance&lt;/te&gt;&lt;/color&gt; trong {1} giây. Trong thời gian này, thời gian tạm dừng và &lt;color=Highlight&gt;Resonator switching&lt;/color&gt; bị vô hiệu hóa. Chỉ có thể thực hiện &lt;color=Highlight&gt;Sublime is the Sun - Sunborne&lt;/color&gt;, &lt;color=Highlight&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt; và &lt;color=Highlight&gt;Dodge&lt;/color&gt; trong trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;. &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; vẫn khả dụng khi ở trên không.
-- Trong trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press}&lt;/color&gt; hoặc &lt;color=Highlight&gt;giữ Normal Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Sublime is the Sun - Sunborne&lt;/color&gt;. Trong trạng thái này, Augusta có thể đi trên mặt nước mà không tốn STA.
+- Trong trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press}&lt;/color&gt; hoặc &lt;color=Highlight&gt;giữ Normal Attack&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Sublime is the Sun - Sunborne&lt;/color&gt;. Trong trạng thái này, Augusta có thể đi trên mặt nước mà không tốn STA.
 - Thực hiện &lt;color=Highlight&gt;environmental, gameplay, or other interactions&lt;/color&gt; sẽ kết thúc &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt; mà không kích hoạt &lt;color=Highlight&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Sublime is the Sun - Sunborne&lt;/color&gt;&lt;/size&gt;
-Gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack. Sau khi thi triển &lt;color=Highlight&gt;Sublime is the Sun - Sunborne&lt;/color&gt; {2} lần, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack or Resonance Liberation&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt;.
+Gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack. Sau khi thi triển &lt;color=Highlight&gt;Sublime is the Sun - Sunborne&lt;/color&gt; {2} lần, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack or Resonance Liberation&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt;&lt;/size&gt;
 Gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack. Thi triển &lt;color=Highlight&gt;Sublime is the Sun - Everbright Protector&lt;/color&gt; sẽ kết thúc trạng thái &lt;color=Highlight&gt;&lt;te href=130606&gt;Sworn Allegiance&lt;/te&gt;&lt;/color&gt; và tiêu hao toàn bộ tầng của &lt;te href=130601&gt;Crown of Wills&lt;/te&gt; sau đó. Tất cả Resonators khác trong đội sẽ bị đưa ra khỏi chiến trường.
@@ -28304,11 +28304,11 @@
       <c r="M375" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Resonance Liberation - Kiếm of Eternal Oath&lt;/color&gt;&lt;/size&gt;
-&lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} và thả Resonance Liberation&lt;/color&gt; để thi triển kỹ năng này.
+&lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} và thả Resonance Liberation&lt;/color&gt; để thi triển kỹ năng này.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Liberation - Sublime is the Sun&lt;/color&gt;&lt;/size&gt;
 Khi Majesty đạt tối đa, &lt;color=Highlight&gt;giữ Resonance Liberation&lt;/color&gt; để thi triển kỹ năng và bước vào trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt; trong {1} giây.
-- Trong trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press}&lt;/color&gt; hoặc &lt;color=Highlight&gt;giữ Normal Attack&lt;/color&gt; để thực hiện tối đa {2} đòn đánh, mở khóa đòn kết thúc mạnh mẽ. Khi ở trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;, &lt;color=Highlight&gt;giữ Resonance Liberation&lt;/color&gt; để thi triển đòn kết thúc sớm.
+- Trong trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press}&lt;/color&gt; hoặc &lt;color=Highlight&gt;giữ Normal Attack&lt;/color&gt; để thực hiện tối đa {2} đòn đánh, mở khóa đòn kết thúc mạnh mẽ. Khi ở trạng thái &lt;color=Highlight&gt;Sworn Allegiance&lt;/color&gt;, &lt;color=Highlight&gt;giữ Resonance Liberation&lt;/color&gt; để thi triển đòn kết thúc sớm.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Majesty&lt;/color&gt;&lt;/size&gt;
 - Augusta nhận 1 tầng Majesty khi thi triển &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Plunge&lt;/color&gt;.
@@ -28737,14 +28737,14 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Undying Sunlight: Strike&lt;/color&gt;&lt;/size&gt;
 Khi &lt;te href=130603&gt;Ascendancy&lt;/te&gt; đạt tối đa, &lt;color=Highlight&gt;Resonance Skill - Warrior's Blade&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Strike&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-- Trong khi thi triển, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack or Resonance Skill&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt;.
+- Trong khi thi triển, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack or Resonance Skill&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt;.
 - &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Strike&lt;/color&gt; có thể được sử dụng lại ngay sau khi bị gián đoạn.
 - &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt; có thể được sử dụng lại sau một khoảng thời gian ngắn nếu bị gián đoạn.
 - Có thể thi triển trên không.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt;&lt;/size&gt;
 Gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;.
-- Trong khi thi triển, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack or Resonance Skill&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Plunge&lt;/color&gt;.
+- Trong khi thi triển, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack or Resonance Skill&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Plunge&lt;/color&gt;.
 - &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt; có thể được sử dụng lại ngay sau khi bị gián đoạn.
 - &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Plunge&lt;/color&gt; có thể được sử dụng lại sau một khoảng thời gian ngắn nếu bị gián đoạn.
 - Chỉ có thể sử dụng khi đang ở trên không.
@@ -28755,8 +28755,8 @@
 - Chỉ có thể sử dụng khi đang ở trên không.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Undying Sunlight: Strike&lt;/color&gt;&lt;/size&gt;
-Khi &lt;te href=130603&gt;Ascendancy&lt;/te&gt; đạt tối đa, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill&lt;/color&gt; sau khi Dodge thành công trên mặt đất hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack or Resonance Skill&lt;/color&gt; sau khi Dodge thành công trên không để sử dụng &lt;color=Highlight&gt;Dodge Counter - Undying Sunlight: Strike&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Resonance Skill.
-- Trong khi thi triển, &lt;color=Highlight&gt;{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack or Resonance Skill&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt;.
+Khi &lt;te href=130603&gt;Ascendancy&lt;/te&gt; đạt tối đa, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill&lt;/color&gt; sau khi Dodge thành công trên mặt đất hoặc &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack or Resonance Skill&lt;/color&gt; sau khi Dodge thành công trên không để sử dụng &lt;color=Highlight&gt;Dodge Counter - Undying Sunlight: Strike&lt;/color&gt;, gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt;, được tính là Sát Thương Resonance Skill.
+- Trong khi thi triển, &lt;color=Highlight&gt;{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack or Resonance Skill&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt;.
 - &lt;color=Highlight&gt;Resonance Skill - Undying Sunlight: Leap&lt;/color&gt; có thể được sử dụng lại sau một khoảng thời gian ngắn nếu bị gián đoạn.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Ascendancy&lt;/color&gt;&lt;/size&gt;
@@ -29186,7 +29186,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -29251,7 +29251,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng Tấn Công {0}, kéo dài trong {1} giây.</t>
+          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng ATK {0}, kéo dài trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -29381,7 +29381,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Khi chịu sát thương, ATK is increased by {0}% và Phòng Ngự tăng {1}% trong 10 giây. Có thể tích lũy tối đa 3 lần.</t>
+          <t>Khi chịu sát thương, ATK tăng {0}% và Phòng Ngự tăng {1}% trong 10 giây. Có thể tích lũy tối đa 3 lần.</t>
         </is>
       </c>
     </row>
@@ -29511,7 +29511,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Tăng Hiệu Ứng Sát Thương Thuộc Tính lên {0}. Mỗi khi sử dụng Intro Skill hoặc Resonance Liberation, tăng Hiệu Ứng Sát Thương Heavy Attack lên {1}, tối đa {2} lần. Hiệu ứng này kéo dài trong {3} giây.</t>
+          <t>Tăng Hiệu Ứng Sát Thương Thuộc Tính lên {0}. Mỗi khi sử dụng Kỹ Năng Khởi Động hoặc Resonance Liberation, tăng Hiệu Ứng Sát Thương Đòn Heavy Attack lên {1}, tối đa {2} lần. Hiệu ứng này kéo dài trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -29706,7 +29706,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Tăng {0} Sát Thương Thuộc Tính. Khi sử dụng Intro Skill, người trang bị nhận được Ageless Marking, tăng {1} Sát Thương Resonance Skill trong {2} giây. Khi sử dụng Resonance Skill, người trang bị nhận được Ethereal Endowment, tăng {3} Sát Thương Resonance Skill trong {4} giây.</t>
+          <t>Tăng {0} Sát Thương Thuộc Tính. Khi sử dụng Kỹ Năng Khởi Động, người trang bị nhận được Ageless Marking, tăng {1} Sát Thương Resonance Skill trong {2} giây. Khi sử dụng Resonance Skill, người trang bị nhận được Ethereal Endowment, tăng {3} Sát Thương Resonance Skill trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Khi HP của Resonator trên {0}, Attack tăng thêm {1}. Khi HP dưới {2}, hồi {3} HP khi gây Sát Thương Basic Attack hoặc Heavy Attack. Hiệu ứng này có thể kích hoạt {5} lần mỗi {4} giây.</t>
+          <t>Khi HP của Resonator trên {0}, ATK tăng thêm {1}. Khi HP dưới {2}, hồi {3} HP khi gây Sát Thương Đòn Cơ Bản hoặc Đòn Heavy Attack. Hiệu ứng này có thể kích hoạt {5} lần mỗi {4} giây.</t>
         </is>
       </c>
     </row>
@@ -29836,7 +29836,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Tăng Attack thêm {0}. Sử dụng Intro Skill hoặc Resonance Liberation sẽ tăng {1} Sát Thương Resonance Liberation trong {2} giây. Gây Sát Thương Heavy Attack sẽ kéo dài hiệu ứng thêm {3} giây, tối đa {4} lần. Mỗi lần kéo dài thành công sẽ tăng {5} Fusion DMG cho toàn bộ Resonators trong đội trong {6} giây. Các hiệu ứng cùng tên không thể chồng chất.</t>
+          <t>Tăng ATK thêm {0}. Sử dụng Kỹ Năng Khởi Động hoặc Resonance Liberation sẽ tăng {1} Sát Thương Resonance Liberation trong {2} giây. Gây Sát Thương Đòn Nặng sẽ kéo dài hiệu ứng thêm {3} giây, tối đa {4} lần. Mỗi lần kéo dài thành công sẽ tăng {5} Sát Thương Fusion cho toàn bộ Resonator trong đội trong {6} giây. Các hiệu ứng cùng tên không thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -29966,7 +29966,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng Tấn Công {0} và Phòng Ngự {1}, kéo dài trong {2} giây.</t>
+          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng ATK {0} và Phòng Ngự {1}, kéo dài trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -30031,7 +30031,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Tăng Hiệu Ứng Sát Thương Basic Attack và Heavy Attack lên {0}.</t>
+          <t>Tăng Hiệu Ứng Sát Thương Đòn Basic Attack và Đòn Heavy Attack lên {0}.</t>
         </is>
       </c>
     </row>
@@ -30096,7 +30096,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng Tấn Công của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
+          <t>Gây DMG lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng ATK của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -30161,7 +30161,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Tấn Công tăng {0}. Khi gây sát thương, Resonator nhận 1 lớp Lông Cháy, có thể kích hoạt mỗi 0.5 giây, và nhận 5 lớp cùng hiệu ứng khi sử dụng Resonance Skill. Mỗi lớp Lông Cháy tăng {1} Sát Thương Resonance Skill, tối đa 14 lớp. Khi đạt tối đa, tất cả lớp sẽ biến mất sau {2} giây.</t>
+          <t>ATK tăng {0}. Khi gây DMG, Cộng Hưởng Giả nhận 1 lớp Lông Cháy, có thể kích hoạt mỗi 0.5 giây, và nhận 5 lớp cùng hiệu ứng khi sử dụng Resonance Skill. Mỗi lớp Lông Cháy tăng {1} Sát Thương Resonance Skill, tối đa 14 lớp. Khi đạt tối đa, tất cả lớp sẽ biến mất sau {2} giây.</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, hồi phục {0} Concerto Energy. Khi Outro Skill được kích hoạt, hồi phục {1} Resonance Energy.</t>
+          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, hồi phục {0} Concerto Energy. Khi Kỹ Năng Outro được kích hoạt, hồi phục {1} Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -30293,7 +30293,7 @@
       <c r="M404" t="inlineStr">
         <is>
           <t>Nhận {0} tầng Hiss khi gây sát thương lên mục tiêu, với {2} tầng được tạo ra mỗi {1} giây.
-Hiss: mỗi tầng tăng Tấn Công của người sử dụng thêm {3} trong {4} giây, tối đa {5} tầng. Chuyển đổi nhân vật sẽ xóa toàn bộ tầng. Khi đạt {6} tầng, Crit. Rate của người sử dụng sẽ tăng thêm {7}.</t>
+Hiss: mỗi tầng tăng ATK của người sử dụng thêm {3} trong {4} giây, tối đa {5} tầng. Chuyển đổi nhân vật sẽ xóa toàn bộ tầng. Khi đạt {6} tầng, Crit. Rate của người sử dụng sẽ tăng thêm {7}.</t>
         </is>
       </c>
     </row>
@@ -30359,8 +30359,8 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Increase Attack thêm {0}. Khi gây sát thương bằng Basic Attack, Resonator nhận thêm {1} Increase Sát Thương Basic Attack trong {2} giây. Hiệu ứng này có thể kích hoạt mỗi giây một lần, tối đa {3} lần.
-Khi tiêu hao Concerto Energy, nhận thêm {4} Increase Sát Thương Basic trong {5} giây. Hiệu ứng này có thể kích hoạt mỗi giây một lần và kết thúc khi Resonator rời khỏi chiến trường.</t>
+          <t>Tăng ATK thêm {0}. Khi gây DMG bằng Đòn Cơ Bản, Cộng Hưởng Giả nhận thêm {1} Tăng Sát Thương Đòn Cơ Bản trong {2} giây. Hiệu ứng này có thể kích hoạt mỗi giây một lần, tối đa {3} lần.
+Khi tiêu hao Concerto Energy, nhận thêm {4} Tăng Sát Thương Cơ Bản trong {5} giây. Hiệu ứng này có thể kích hoạt mỗi giây một lần và kết thúc khi Cộng Hưởng Giả rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -30425,7 +30425,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Khi hồi phục, tăng Sát Thương Resonance Skill thêm {0} trong {1} giây. Khi Rover: Aero sử dụng Resonance Skill Unbound Flow, Aero DMG gây ra bởi Resonators gần đó trên chiến trường sẽ được Khuếch Đại thêm {2} trong {3} giây.</t>
+          <t>Khi hồi phục, tăng Sát Thương Resonance Skill thêm {0} trong {1} giây. Khi Rover: Aero sử dụng Resonance Skill Unbound Flow, Sát Thương Aero gây ra bởi các Resonator gần đó trên chiến trường sẽ được Khuếch Đại thêm {2} trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>HP tối đa tăng thêm {0}. Trong {3} giây sau khi sử dụng Intro Skill hoặc Basic Attack, bỏ qua {1} Phòng Ngự của mục tiêu khi gây sát thương. Nếu mục tiêu có ít nhất 1 lớp Erosion Gió, sát thương nhận vào sẽ được Khuếch Đại thêm {2}.</t>
+          <t>HP tối đa tăng thêm {0}. Trong {3} giây sau khi sử dụng Kỹ Năng Khởi Động hoặc Đòn Cơ Bản, bỏ qua {1} Phòng Ngự của mục tiêu khi gây DMG. Nếu mục tiêu có ít nhất 1 lớp Aero Erosion, DMG nhận vào sẽ được Khuếch Đại thêm {2}.</t>
         </is>
       </c>
     </row>
@@ -30555,7 +30555,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng Tấn Công của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
+          <t>Gây DMG lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng ATK của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -30620,7 +30620,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Tăng Tái Tạo Năng Lượng thêm {0}. Tấn Công của Resonator đến sẽ được tăng {1} trong {3} giây, có thể chồng chất lên đến {2} lần sau khi người sử dụng kích hoạt Outro Skill.</t>
+          <t>Tăng Tái Tạo Năng Lượng thêm {0}. ATK của Resonator đến sẽ được tăng {1} trong {3} giây, có thể chồng chất lên đến {2} lần sau khi người sử dụng kích hoạt Kỹ Năng Outro.</t>
         </is>
       </c>
     </row>
@@ -30685,7 +30685,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công thêm {0}. Mỗi lần sử dụng Intro Skill hoặc Resonance Liberation, Sát Thương Resonance Skill sẽ tăng thêm {1} trong {2} giây.</t>
+          <t>Tăng ATK thêm {0}. Mỗi lần sử dụng Kỹ Năng Khởi Động hoặc Resonance Liberation, Sát Thương Resonance Skill sẽ tăng thêm {1} trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -30750,7 +30750,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate thêm {0}. Khi kích hoạt Resonance Liberation, nhận thêm {1} Basic Attack trong {2} giây. Gây Sát Thương bằng Basic Attack sẽ nhận thêm {3} Basic Attack trong {4} giây.</t>
+          <t>Tăng Crit. Rate thêm {0}. Khi kích hoạt Resonance Liberation, nhận thêm {1} Basic Attack trong {2} giây. Gây Sát Thương bằng Basic Attack sẽ nhận thêm {3} Basic Attack trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -30815,7 +30815,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>ATK is increased by {0}. Gây Aero Erosion lên mục tiêu sẽ tăng {1} Aero DMG trong {2} giây. Đánh trúng mục tiêu bị Aero Erosion sẽ giảm {3} Aero RES của chúng trong {4} giây. Hiệu ứng cùng tên không thể cộng dồn.</t>
+          <t>ATK tăng {0}. Gây Aero Erosion lên mục tiêu sẽ tăng {1} Sát Thương Aero trong {2} giây. Đánh trúng mục tiêu bị Aero Erosion sẽ giảm {3} Kháng Aero của chúng trong {4} giây. Hiệu ứng cùng tên không thể cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -31014,7 +31014,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng Tấn Công của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
+          <t>Gây DMG lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng ATK của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -31211,7 +31211,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Tăng Attack thêm {0}. Mỗi lần sử dụng Basic Attack hoặc Intro Skill, Sát Thương Heavy Attack sẽ tăng thêm {1} trong {2} giây.</t>
+          <t>Tăng ATK thêm {0}. Mỗi lần sử dụng Basic Attack hoặc Kỹ Năng Khởi Động, Sát Thương Đòn Nặng sẽ tăng thêm {1} trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -31276,7 +31276,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Tăng Attack {0}. Khi sử dụng Basic Attack, sẽ kích hoạt các hiệu ứng sau: Gây sát thương bỏ qua {1} Phòng Ngự của mục tiêu và Khuếch Đại Spectro DMG Frazzle thêm {2} trong {3} giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian tác dụng.</t>
+          <t>Tăng ATK {0}. Khi sử dụng Đòn Basic Attack, sẽ kích hoạt các hiệu ứng sau: Gây DMG bỏ qua {1} Phòng Ngự của mục tiêu và Khuếch Đại Sát Thương Spectro Frazzle thêm {2} trong {3} giây. Kích hoạt lại hiệu ứng sẽ làm mới thời gian tác dụng.</t>
         </is>
       </c>
     </row>
@@ -31341,7 +31341,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng Tấn Công lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
+          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng ATK lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng Tấn Công của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
+          <t>Gây DMG lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng ATK của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -31672,7 +31672,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Hiệu Quả Healing của Resonator lên {0} trong {1} giây.</t>
+          <t>Kích hoạt Resonance Liberation tăng Hiệu Quả Hồi Phục của Resonator lên {0} trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -31737,7 +31737,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Increase Attack thêm {0}. Khi Resonator đang trên chiến trường, sử dụng Resonance Skill sẽ nhận thêm {1} Increase Sát Thương Basic Attack, tối đa {2} lần trong {3} giây. Khi đạt {4} lần tích lũy trở lên, kích hoạt Outro Skill sẽ tiêu hao toàn bộ hiệu ứng này và cộng thêm {5} Increase Sát Thương Basic Attack trong {6} giây, hiệu lực ngay cả khi Resonator rời khỏi chiến trường.</t>
+          <t>Tăng ATK thêm {0}. Khi Cộng Hưởng Giả đang trên chiến trường, sử dụng Resonance Skill sẽ nhận thêm {1} Tăng Sát Thương Đòn Cơ Bản, tối đa {2} lần trong {3} giây. Khi đạt {4} lần tích lũy trở lên, kích hoạt Kỹ Năng Outro sẽ tiêu hao toàn bộ hiệu ứng này và cộng thêm {5} Tăng Sát Thương Đòn Cơ Bản trong {6} giây, hiệu lực ngay cả khi Cộng Hưởng Giả rời khỏi chiến trường.</t>
         </is>
       </c>
     </row>
@@ -31802,7 +31802,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch đang mang Hỗn Loạn Quang sẽ tăng Sát Thương Quang của người sử dụng thêm {0}, nhận 1 tầng mỗi giây trong 6 giây, tối đa 4 tầng.</t>
+          <t>Gây DMG lên kẻ địch đang mang Hỗn Loạn Quang sẽ tăng Sát Thương Quang của người sử dụng thêm {0}, nhận 1 tầng mỗi giây trong 6 giây, tối đa 4 tầng.</t>
         </is>
       </c>
     </row>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Increase Attack thêm {0}. Khi gây sát thương lên mục tiêu bị Spectro Frazzle, Resonator nhận thêm {1} Increase Sát Thương Basic Attack và {1} Increase Sát Thương Heavy Attack, có thể tích lũy tối đa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} trong {3} giây. Kích hoạt Outro Skill sẽ khuếch đại Spectro DMG Frazzle lên các mục tiêu xung quanh Resonator hiện tại thêm {4} trong {5} giây. Hiệu ứng cùng tên không thể chồng chất.</t>
+          <t>Tăng ATK thêm {0}. Khi gây DMG lên mục tiêu bị Spectro Frazzle, Resonator nhận thêm {1} Tăng Sát Thương Đòn Cơ Bản và {1} Tăng Sát Thương Đòn Nặng, có thể tích lũy tối đa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} trong {3} giây. Kích hoạt Kỹ Năng Outro sẽ khuếch đại DMG Spectro Frazzle lên các mục tiêu xung quanh Resonator hiện tại thêm {4} trong {5} giây. Hiệu ứng cùng tên không thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -31934,9 +31934,9 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Tăng Attack thêm {0}. Khi sử dụng Kỹ Năng Echoes trong vòng {1} giây sau khi dùng Intro Skill hoặc Basic Attack, nhận được &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp Gentle Dream}. Các Echoes cùng tên chỉ kích hoạt hiệu ứng này một lần, tối đa {3} lớp, duy trì trong {4} giây. Khi đạt 2 lớp, sử dụng Kỹ Năng Echoes sẽ không làm mới thời gian hiệu ứng. Hiệu ứng kích hoạt tối đa một lần mỗi 10 giây. Chuyển đổi Resonator sẽ kết thúc hiệu ứng sớm.
+          <t>Tăng ATK thêm {0}. Khi sử dụng Kỹ Năng Echo trong vòng {1} giây sau khi dùng Kỹ Năng Khởi Động hoặc Basic Attack, nhận được &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp Gentle Dream}. Các Echo cùng tên chỉ kích hoạt hiệu ứng này một lần, tối đa {3} lớp, duy trì trong {4} giây. Khi đạt 2 lớp, sử dụng Kỹ Năng Echo sẽ không làm mới thời gian hiệu ứng. Hiệu ứng kích hoạt tối đa một lần mỗi 10 giây. Chuyển đổi Resonator sẽ kết thúc hiệu ứng sớm.
 Khi có &lt;SapTag=5&gt;{5}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp}: Tăng {6} Sát Thương Basic Attack.
-Khi có &lt;SapTag=7&gt;{7}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp}: Bỏ qua {8} Havoc RES của mục tiêu.</t>
+Khi có &lt;SapTag=7&gt;{7}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp}: Bỏ qua {8} Kháng Havoc của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Tấn Công tăng thêm {0}. Trong vòng {1} giây sau khi gây Sát Thương Kỹ Năng Vang Âm, nhận thêm {2} Sát Thương Resonance Skill và {3} DMG Amplification Kỹ Năng Vang Âm, đồng thời bỏ qua {4} Phòng Ngự của mục tiêu khi gây sát thương.</t>
+          <t>ATK tăng thêm {0}. Trong vòng {1} giây sau khi gây Sát Thương Kỹ Năng Vang Âm, nhận thêm {2} Sát Thương Resonance Skill và {3} Khuếch Đại Sát Thương Kỹ Năng Vang Âm, đồng thời bỏ qua {4} Phòng Ngự của mục tiêu khi gây DMG.</t>
         </is>
       </c>
     </row>
@@ -32066,7 +32066,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Tăng Attack thêm {0}. Sử dụng Intro Skill hoặc Resonance Skill sẽ tăng {1} Sát Thương Heavy Attack trong {2} giây. Khi có Shield, Sát Thương Heavy Attack sẽ bỏ qua {3} Phòng Ngự của mục tiêu trong {5} giây, tối đa {4} lớp. Hiệu ứng kích hoạt mỗi 0.5 giây một lần.</t>
+          <t>Tăng ATK thêm {0}. Sử dụng Kỹ Năng Khởi Động hoặc Resonance Skill sẽ tăng {1} Sát Thương Đòn Nặng trong {2} giây. Khi có Khiên, Sát Thương Đòn Nặng sẽ bỏ qua {3} Phòng Ngự của mục tiêu trong {5} giây, tối đa {4} lớp. Hiệu ứng kích hoạt mỗi 0.5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -32131,7 +32131,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công thêm {0}. Sử dụng Intro Skill hoặc Resonance Liberation sẽ tăng {1} Sát Thương Resonance Liberation trong {2} giây. Khi có Shield, Sát Thương Resonance Liberation sẽ bỏ qua {3} Phòng Ngự của mục tiêu trong {6} giây, tối đa {5} lớp. Hiệu ứng kích hoạt mỗi {4} giây một lần. Khi dùng Intro Skill, hiệu ứng đạt tối đa ngay lập tức và duy trì trong {7} giây.</t>
+          <t>Tăng ATK thêm {0}. Sử dụng Kỹ Năng Khởi Động hoặc Resonance Liberation sẽ tăng {1} Sát Thương Resonance Liberation trong {2} giây. Khi có Khiên, Sát Thương Resonance Liberation sẽ bỏ qua {3} Phòng Ngự của mục tiêu trong {6} giây, tối đa {5} lớp. Hiệu ứng kích hoạt mỗi {4} giây một lần. Khi dùng Kỹ Năng Khởi Động, hiệu ứng đạt tối đa ngay lập tức và duy trì trong {7} giây.</t>
         </is>
       </c>
     </row>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Dòng "Vũ Khí Tổng Hợp" của Spacetrek Collective
+          <t>Dòng "Vũ Khí Tổng Hợp" của Tập Đoàn Spacetrek
 Mẫu: SCSA-LHRi-BB325042
 Được rèn từ công nghệ phức hợp kết hợp các thành phần sinh học Exostrider với Tacetite, vũ khí này sở hữu hai đặc tính cốt lõi: tự điều chỉnh tần số và liên kết với người sử dụng. Sức mạnh của nó tỷ lệ thuận với Forte của người sử dụng, trở nên sắc bén hơn qua quá trình rèn luyện Forte chuyên sâu.
 Các hoa văn ánh sáng dọc lưỡi kiếm thay đổi theo sự dao động tần số của người sử dụng. Nó kết tinh lý trí thành một sức mạnh tập trung—vừa là công cụ để phá vỡ chướng ngại, vừa là thước đo để khám phá những điều chưa biết. Hoàn hảo cho những kẻ phá vỡ giới hạn, những người tự khắc họa con đường bằng ý chí kiên định.</t>
@@ -32752,7 +32752,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng Tấn Công của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
+          <t>Gây DMG lên kẻ địch đang mang hiệu ứng Tiêu Cực sẽ tăng ATK của người sử dụng thêm {0} trong {1} giây. Hiệu ứng này kích hoạt tối đa 1 lần mỗi giây, có thể chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -33369,7 +33369,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Khi nhận sát thương, Tấn Công tăng {0}% và Phòng Ngự tăng {1}%, hiệu ứng kéo dài 10 giây và có thể chồng chất lên đến 3 lần.</t>
+          <t>Khi nhận sát thương, ATK tăng {0}% và Phòng Ngự tăng {1}%, hiệu ứng kéo dài 10 giây và có thể chồng chất lên đến 3 lần.</t>
         </is>
       </c>
     </row>
@@ -33434,7 +33434,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Trong vòng {0} giây sau khi sử dụng Resonance Skill, Tấn Công tăng {2} sau mỗi {1} giây, tối đa {3} lần. Hiệu ứng này có thể kích hoạt {5} lần mỗi {4} giây. Khi đạt {6} lần cộng dồn, tất cả sẽ được đặt lại trong {7} giây.</t>
+          <t>Trong vòng {0} giây sau khi sử dụng Resonance Skill, ATK tăng {2} sau mỗi {1} giây, tối đa {3} lần. Hiệu ứng này có thể kích hoạt {5} lần mỗi {4} giây. Khi đạt {6} lần cộng dồn, tất cả sẽ được đặt lại trong {7} giây.</t>
         </is>
       </c>
     </row>
@@ -33499,7 +33499,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Tăng Attack thêm {0} khi gây Sát Thương Basic Attack hoặc Heavy Attack, có thể tích lũy tối đa {1} lần. Hiệu ứng này kéo dài trong {2} giây và có thể kích hoạt {4} lần mỗi {3} giây.</t>
+          <t>Tăng ATK thêm {0} khi gây Sát Thương Đòn Basic Attack hoặc Đòn Heavy Attack, có thể tích lũy tối đa {1} lần. Hiệu ứng này kéo dài trong {2} giây và có thể kích hoạt {4} lần mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -33564,7 +33564,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng Tấn Công lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
+          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng ATK lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -33629,7 +33629,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -33694,7 +33694,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -33759,7 +33759,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng Tấn Công {0}, kéo dài trong {1} giây.</t>
+          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng ATK {0}, kéo dài trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, Sát Thương của Basic Attack và Đòn Tấn Công Nặng tăng {0}% trong 10 giây.</t>
+          <t>Sau khi sử dụng Resonance Liberation, Sát Thương của Đòn Basic Attack và Đòn Heavy Attack tăng {0}% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -34019,7 +34019,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Tăng Tái Tạo Năng Lượng thêm {0}. Khi kích hoạt Resonance Skill, tăng Tấn Công thêm {1}, có thể chồng chất lên đến {2} lần. Hiệu ứng này kéo dài trong {3} giây.</t>
+          <t>Tăng Tái Tạo Năng Lượng thêm {0}. Khi kích hoạt Resonance Skill, tăng ATK thêm {1}, có thể chồng chất lên đến {2} lần. Hiệu ứng này kéo dài trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -34279,7 +34279,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Khi HP của Resonator giảm xuống dưới {0}, Sát Thương Heavy Attack tăng thêm {1} và hồi {2} HP khi gây Sát Thương Heavy Attack. Hiệu ứng này có thể kích hoạt {4} lần mỗi {3} giây.</t>
+          <t>Khi HP của Resonator giảm xuống dưới {0}, Sát Thương Đòn Heavy Attack tăng thêm {1} và hồi {2} HP khi gây Sát Thương Đòn Heavy Attack. Hiệu ứng này có thể kích hoạt {4} lần mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -34409,7 +34409,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng Tấn Công {0}, kéo dài trong {1} giây.</t>
+          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng ATK {0}, kéo dài trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -34539,7 +34539,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Khi dùng Resonance Liberation, Sát Thương Basic Attack và Heavy Attack tăng {0}% trong 10 giây.</t>
+          <t>Khi dùng Resonance Liberation, Sát Thương Đòn Cơ Bản và Đòn Nặng tăng {0}% trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -34604,7 +34604,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Resonator được trang bị nhận {0} tầng Lời Thề khi vào chiến trường. Mỗi tầng tăng Tấn Công thêm {1}, tối đa {2} tầng. Hiệu ứng này có thể kích hoạt {4} lần mỗi {3} giây. Resonator mất {6} tầng Lời Thề sau mỗi {5} giây và nhận {7} tầng khi đánh bại kẻ địch.</t>
+          <t>Resonator được trang bị nhận {0} tầng Lời Thề khi vào chiến trường. Mỗi tầng tăng ATK thêm {1}, tối đa {2} tầng. Hiệu ứng này có thể kích hoạt {4} lần mỗi {3} giây. Resonator mất {6} tầng Lời Thề sau mỗi {5} giây và nhận {7} tầng khi đánh bại kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng Tấn Công lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
+          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng ATK lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -34799,7 +34799,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -34864,7 +34864,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -34929,7 +34929,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng Tấn Công {0}, kéo dài trong {1} giây.</t>
+          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng ATK {0}, kéo dài trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -34994,7 +34994,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Liberation, ATK is increased by {0}% trong 12 giây.</t>
+          <t>Sau khi sử dụng Resonance Liberation, ATK tăng {0}% trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -35254,7 +35254,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Khi sử dụng Dodge Counter, hồi {0} HP tối đa của Resonator. Hiệu ứng này có thể kích hoạt {2} lần mỗi {1} giây.</t>
+          <t>Khi sử dụng Dodge Counter Tránh, hồi {0} HP tối đa của Resonator. Hiệu ứng này có thể kích hoạt {2} lần mỗi {1} giây.</t>
         </is>
       </c>
     </row>
@@ -35384,7 +35384,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Khi Resonator không chịu sát thương, Tấn Công tăng thêm {1} sau mỗi {0} giây, có thể chồng chất lên đến {2} lần. Hiệu ứng này kéo dài {3} giây. Khi Resonator chịu sát thương, sẽ mất {4} lượt chồng chất và hồi {5} HP tối đa.</t>
+          <t>Khi Resonator không chịu sát thương, ATK tăng thêm {1} sau mỗi {0} giây, có thể chồng chất lên đến {2} lần. Hiệu ứng này kéo dài {3} giây. Khi Resonator chịu sát thương, sẽ mất {4} lượt chồng chất và hồi {5} HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -35644,7 +35644,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Khi dùng Resonance Liberation, ATK is increased by {0}% trong 12 giây.</t>
+          <t>Khi dùng Resonance Liberation, ATK tăng {0}% trong 12 giây.</t>
         </is>
       </c>
     </row>
@@ -35709,7 +35709,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Khi Resonator chạy hoặc Dodge, Tấn Công tăng {0}, tối đa {2} lần. Hiệu ứng kéo dài {1} giây.</t>
+          <t>Khi Resonator chạy hoặc né tránh, ATK tăng {0}, tối đa {2} lần. Hiệu ứng kéo dài {1} giây.</t>
         </is>
       </c>
     </row>
@@ -35774,7 +35774,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Khi đánh trúng mục tiêu bằng Basic Attack hoặc Đòn Tấn Công Nặng, tăng Sát Thương Resonance Skill thêm {0}, chồng chất tối đa {1} lần. Hiệu ứng kéo dài {2} giây và có thể kích hoạt {4} lần mỗi {3} giây.</t>
+          <t>Khi đánh trúng mục tiêu bằng Đòn Basic Attack hoặc Đòn Heavy Attack, tăng Sát Thương Resonance Skill thêm {0}, chồng chất tối đa {1} lần. Hiệu ứng kéo dài {2} giây và có thể kích hoạt {4} lần mỗi {3} giây.</t>
         </is>
       </c>
     </row>
@@ -35839,7 +35839,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng Tấn Công lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
+          <t>Kích hoạt Resonance Skill sẽ nhận {0} Resonance Energy và tăng ATK lên {1}, kéo dài {2} giây. Hiệu ứng này chỉ kích hoạt mỗi {3} giây một lần.</t>
         </is>
       </c>
     </row>
@@ -35904,7 +35904,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -35969,7 +35969,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Tăng ATK thêm {0}.</t>
+          <t>Tăng ATK {0}.</t>
         </is>
       </c>
     </row>
@@ -36034,7 +36034,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng Tấn Công {0}, kéo dài trong {1} giây.</t>
+          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng ATK {0}, kéo dài trong {1} giây.</t>
         </is>
       </c>
     </row>
@@ -36099,7 +36099,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Resonance Skill, Đòn Tấn Công Nặng bỏ qua {0}% Phòng Ngự của mục tiêu trong 8 giây.</t>
+          <t>Sau khi sử dụng Resonance Skill, Đòn Heavy Attack bỏ qua {0}% Phòng Ngự của mục tiêu trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -36294,7 +36294,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Tăng Tái Tạo Năng Lượng thêm {0}. Khi trúng mục tiêu bằng Resonance Skill, tăng Sát Thương Basic Attack thêm {1}, kéo dài trong {2} giây. Khi trúng mục tiêu bằng Basic Attack, tăng Sát Thương Resonance Skill thêm {3}, kéo dài trong {4} giây.</t>
+          <t>Tăng Tái Tạo Năng Lượng thêm {0}. Khi trúng mục tiêu bằng Resonance Skill, tăng Sát Thương Đòn Basic Attack thêm {1}, kéo dài trong {2} giây. Khi trúng mục tiêu bằng Đòn Basic Attack, tăng Sát Thương Resonance Skill thêm {3}, kéo dài trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -36554,7 +36554,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Khi Resonator chạy hoặc Dodge, Tấn Công tăng {0}. Sát Thương Dodge Counter tăng {1}, kéo dài {2} giây. Khi thực hiện Dodge Counter, hồi {3} HP tối đa. Hiệu ứng này có thể kích hoạt {5} lần mỗi {4} giây.</t>
+          <t>Khi Resonator chạy hoặc né tránh, ATK tăng {0}. Sát Thương Dodge Counter tăng {1}, kéo dài {2} giây. Khi thực hiện Dodge Counter, hồi {3} HP tối đa. Hiệu ứng này có thể kích hoạt {5} lần mỗi {4} giây.</t>
         </is>
       </c>
     </row>
@@ -36684,7 +36684,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng Sát Thương Resonance Liberation {0}, kéo dài trong {1} giây.</t>
+          <t>Khi Kỹ Năng Giới Thiệu được kích hoạt, tăng Sát Thương Giải Cứu Cộng Hưởng {0}, kéo dài trong {1} giây.</t>
         </is>
       </c>
     </row>
